--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -14809,7 +14809,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -14848,581 +14848,12 @@
         <v>ملاحظات</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>30</v>
-      </c>
-      <c r="B3" t="str">
-        <v>ابو السعود معاوية ابو السعود</v>
-      </c>
-      <c r="C3" t="str">
-        <v>حارس</v>
-      </c>
-      <c r="D3" t="str">
-        <v>متوسط وثانوي</v>
-      </c>
-      <c r="E3" t="str">
-        <v>بنات</v>
-      </c>
-      <c r="F3" t="str">
-        <v>2474277379</v>
-      </c>
-      <c r="G3" t="str">
-        <v>السودان</v>
-      </c>
-      <c r="H3" t="str">
-        <v>0554292056</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>295</v>
-      </c>
-      <c r="B4" t="str">
-        <v>صبري محمد محمود عثمان</v>
-      </c>
-      <c r="C4" t="str">
-        <v>حارس</v>
-      </c>
-      <c r="D4" t="str">
-        <v>ثانوي بنين</v>
-      </c>
-      <c r="E4" t="str">
-        <v xml:space="preserve">بنين </v>
-      </c>
-      <c r="F4" t="str">
-        <v>2207392172</v>
-      </c>
-      <c r="H4" t="str">
-        <v>553833279</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>293</v>
-      </c>
-      <c r="B5" t="str">
-        <v>عاطف محمد ادريس محمد</v>
-      </c>
-      <c r="C5" t="str">
-        <v>حارس</v>
-      </c>
-      <c r="D5" t="str">
-        <v>أقسام البنين</v>
-      </c>
-      <c r="E5" t="str">
-        <v xml:space="preserve">بنين </v>
-      </c>
-      <c r="F5" t="str">
-        <v>2276755655</v>
-      </c>
-      <c r="G5" t="str">
-        <v>السودان</v>
-      </c>
-      <c r="H5" t="str">
-        <v>552178464</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3028</v>
-      </c>
-      <c r="B6" t="str">
-        <v>ابوبكر صديق</v>
-      </c>
-      <c r="C6" t="str">
-        <v>سائق</v>
-      </c>
-      <c r="D6" t="str">
-        <v>كل المراحل</v>
-      </c>
-      <c r="E6" t="str">
-        <v>بنات</v>
-      </c>
-      <c r="F6" t="str">
-        <v>2539904892</v>
-      </c>
-      <c r="G6" t="str">
-        <v>بنجلاديش</v>
-      </c>
-      <c r="H6" t="str">
-        <v>0571650836</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>324</v>
-      </c>
-      <c r="B7" t="str">
-        <v>صابير جولا</v>
-      </c>
-      <c r="C7" t="str">
-        <v>سائق</v>
-      </c>
-      <c r="D7" t="str">
-        <v>كل المراحل</v>
-      </c>
-      <c r="E7" t="str">
-        <v>بنات</v>
-      </c>
-      <c r="F7">
-        <v>2429034354</v>
-      </c>
-      <c r="G7" t="str">
-        <v>نيبالي</v>
-      </c>
-      <c r="H7" t="str">
-        <v>500798824</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>3442</v>
-      </c>
-      <c r="B8" t="str">
-        <v>فيضان احمد</v>
-      </c>
-      <c r="C8" t="str">
-        <v>سائق</v>
-      </c>
-      <c r="D8" t="str">
-        <v>كل المراحل</v>
-      </c>
-      <c r="E8" t="str">
-        <v>بنات</v>
-      </c>
-      <c r="F8" t="str">
-        <v>2555671813</v>
-      </c>
-      <c r="G8" t="str">
-        <v>الهند</v>
-      </c>
-      <c r="H8" t="str">
-        <v>0575249055</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>3441</v>
-      </c>
-      <c r="B9" t="str">
-        <v>محمد علي</v>
-      </c>
-      <c r="C9" t="str">
-        <v>سائق</v>
-      </c>
-      <c r="D9" t="str">
-        <v>كل المراحل</v>
-      </c>
-      <c r="E9" t="str">
-        <v xml:space="preserve">بنين </v>
-      </c>
-      <c r="F9" t="str">
-        <v>2555671722</v>
-      </c>
-      <c r="G9" t="str">
-        <v>الهند</v>
-      </c>
-      <c r="H9" t="str">
-        <v>0571187133</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>319</v>
-      </c>
-      <c r="B10" t="str">
-        <v>نجم الدين خان</v>
-      </c>
-      <c r="C10" t="str">
-        <v>سائق</v>
-      </c>
-      <c r="D10" t="str">
-        <v>كل المراحل</v>
-      </c>
-      <c r="E10" t="str">
-        <v>بنات</v>
-      </c>
-      <c r="F10" t="str">
-        <v>2429347194</v>
-      </c>
-      <c r="G10" t="str">
-        <v>نيبالي</v>
-      </c>
-      <c r="H10" t="str">
-        <v>0576104814</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>4625</v>
-      </c>
-      <c r="B11" t="str">
-        <v>نادر محمد عبد الهادي</v>
-      </c>
-      <c r="C11" t="str">
-        <v>سائق</v>
-      </c>
-      <c r="D11" t="str">
-        <v>الابتدائي والمتوسط</v>
-      </c>
-      <c r="E11" t="str">
-        <v>بنات</v>
-      </c>
-      <c r="F11" t="str">
-        <v>2615293293</v>
-      </c>
-      <c r="G11" t="str">
-        <v>مصر</v>
-      </c>
-      <c r="H11" t="str">
-        <v>0544388592</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="str">
-        <v>عتيق آل رامان</v>
-      </c>
-      <c r="C12" t="str">
-        <v>سائق</v>
-      </c>
-      <c r="D12" t="str">
-        <v>كل المراحل</v>
-      </c>
-      <c r="E12" t="str">
-        <v>بنات</v>
-      </c>
-      <c r="F12" t="str">
-        <v>2552787216</v>
-      </c>
-      <c r="G12" t="str">
-        <v>الهند</v>
-      </c>
-      <c r="H12" t="str">
-        <v>0572188404</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>322</v>
-      </c>
-      <c r="B13" t="str">
-        <v>رانجيت مهاسيز</v>
-      </c>
-      <c r="C13" t="str">
-        <v>عامل نظافة</v>
-      </c>
-      <c r="D13" t="str">
-        <v>الثانوية</v>
-      </c>
-      <c r="E13" t="str">
-        <v xml:space="preserve">بنين </v>
-      </c>
-      <c r="F13" t="str">
-        <v>2428894089</v>
-      </c>
-      <c r="G13" t="str">
-        <v>نيبالي</v>
-      </c>
-      <c r="H13" t="str">
-        <v>0557887356</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>315</v>
-      </c>
-      <c r="B14" t="str">
-        <v>شهيد الإسلام أنو مياه</v>
-      </c>
-      <c r="C14" t="str">
-        <v>عامل نظافة</v>
-      </c>
-      <c r="D14" t="str">
-        <v>الابتدائية</v>
-      </c>
-      <c r="E14" t="str">
-        <v xml:space="preserve">بنين </v>
-      </c>
-      <c r="F14" t="str">
-        <v>2268093669</v>
-      </c>
-      <c r="G14" t="str">
-        <v>بنجلاديش</v>
-      </c>
-      <c r="H14" t="str">
-        <v>530195994</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>321</v>
-      </c>
-      <c r="B15" t="str">
-        <v>بابلو مهاسيز</v>
-      </c>
-      <c r="C15" t="str">
-        <v>عامل نظافة</v>
-      </c>
-      <c r="D15" t="str">
-        <v>الابتدائية</v>
-      </c>
-      <c r="E15" t="str">
-        <v xml:space="preserve">بنين </v>
-      </c>
-      <c r="F15" t="str">
-        <v>2428894311</v>
-      </c>
-      <c r="G15" t="str">
-        <v>نيبالي</v>
-      </c>
-      <c r="H15" t="str">
-        <v>0572556532</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>328</v>
-      </c>
-      <c r="B16" t="str">
-        <v>نور الحق اكي اولادير</v>
-      </c>
-      <c r="C16" t="str">
-        <v>عامل نظافة</v>
-      </c>
-      <c r="D16" t="str">
-        <v>الثانوية</v>
-      </c>
-      <c r="E16" t="str">
-        <v xml:space="preserve">بنين </v>
-      </c>
-      <c r="F16" t="str">
-        <v>2432179014</v>
-      </c>
-      <c r="G16" t="str">
-        <v>بنجلاديش</v>
-      </c>
-      <c r="H16" t="str">
-        <v>572293461</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>329</v>
-      </c>
-      <c r="B17" t="str">
-        <v>جيرالد اوغستين</v>
-      </c>
-      <c r="C17" t="str">
-        <v>عامل نظافة</v>
-      </c>
-      <c r="D17" t="str">
-        <v>إدارة المجمع</v>
-      </c>
-      <c r="E17" t="str">
-        <v xml:space="preserve">بنين </v>
-      </c>
-      <c r="F17" t="str">
-        <v>2443914516</v>
-      </c>
-      <c r="G17" t="str">
-        <v>الفلبين</v>
-      </c>
-      <c r="H17" t="str">
-        <v>573082979</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>341</v>
-      </c>
-      <c r="B18" t="str">
-        <v>لوسيلا نينادا كابانيرو</v>
-      </c>
-      <c r="C18" t="str">
-        <v>عاملة نظافة</v>
-      </c>
-      <c r="D18" t="str">
-        <v>الثانوية</v>
-      </c>
-      <c r="E18" t="str">
-        <v>بنات</v>
-      </c>
-      <c r="F18" t="str">
-        <v>2444621433</v>
-      </c>
-      <c r="G18" t="str">
-        <v>الفلبين</v>
-      </c>
-      <c r="H18" t="str">
-        <v>503306948</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>344</v>
-      </c>
-      <c r="B19" t="str">
-        <v>ميشيل كالدو توبالاس</v>
-      </c>
-      <c r="C19" t="str">
-        <v>عاملة نظافة</v>
-      </c>
-      <c r="D19" t="str">
-        <v>التمهيدية</v>
-      </c>
-      <c r="E19" t="str">
-        <v>بنات</v>
-      </c>
-      <c r="F19" t="str">
-        <v>2442596603</v>
-      </c>
-      <c r="G19" t="str">
-        <v>الفلبين</v>
-      </c>
-      <c r="H19" t="str">
-        <v>570456403</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="str">
-        <v>الوظيفة / المرحلة</v>
-      </c>
-      <c r="C21" t="str">
-        <v>تمهيدي</v>
-      </c>
-      <c r="D21" t="str">
-        <v>ابتدائي بنات</v>
-      </c>
-      <c r="E21" t="str">
-        <v>ابتدائي بنين</v>
-      </c>
-      <c r="F21" t="str">
-        <v>متوسط بنات</v>
-      </c>
-      <c r="G21" t="str">
-        <v>ثانوي بنين</v>
-      </c>
-      <c r="H21" t="str">
-        <v>ثانوي بنات</v>
-      </c>
-      <c r="I21" t="str">
-        <v>ادارة المجمع</v>
-      </c>
-      <c r="J21" t="str">
-        <v>الاجمالي</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" t="str">
-        <v>عامل نظافة</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="E22">
-        <v>2</v>
-      </c>
-      <c r="G22">
-        <v>2</v>
-      </c>
-      <c r="H22">
-        <v>1</v>
-      </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-      <c r="J22">
-        <f>SUM(C22:I22)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="str">
-        <v>حارس</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-      <c r="H23">
-        <v>1</v>
-      </c>
-      <c r="J23">
-        <f>SUM(C23:I23)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="str">
-        <v>سائق</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24">
-        <v>2</v>
-      </c>
-      <c r="E24">
-        <v>1</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="H24">
-        <v>2</v>
-      </c>
-      <c r="J24">
-        <f>SUM(C24:I24)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="str">
-        <v>إجمالي الخدمات المساندة أفراد</v>
-      </c>
-      <c r="C25">
-        <f>SUM(C22:C24)</f>
-        <v>2</v>
-      </c>
-      <c r="D25">
-        <f>SUM(D22:D24)</f>
-        <v>2</v>
-      </c>
-      <c r="E25">
-        <f>SUM(E22:E24)</f>
-        <v>4</v>
-      </c>
-      <c r="F25">
-        <f>SUM(F22:F24)</f>
-        <v>1</v>
-      </c>
-      <c r="G25">
-        <f>SUM(G22:G24)</f>
-        <v>3</v>
-      </c>
-      <c r="H25">
-        <f>SUM(H22:H24)</f>
-        <v>4</v>
-      </c>
-      <c r="I25">
-        <f>SUM(I22:I24)</f>
-        <v>1</v>
-      </c>
-      <c r="J25">
-        <f>SUM(C25:I25)</f>
-        <v>17</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
-  <pageMargins left="0.15748031496062992" right="0.15748031496062992" top="0.4330708661417323" bottom="0.2" header="0.31496062992125984" footer="0.17"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -26,6 +26,7 @@
     <sheet name="القدرات والتحصيلي" sheetId="21" r:id="rId21"/>
     <sheet name="تصنيف العاملين " sheetId="22" r:id="rId22"/>
     <sheet name="العهدة المالية" sheetId="23" r:id="rId23"/>
+    <sheet name="الاسنادات" sheetId="24" r:id="rId24"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'إحصاء التخصصات'!#REF!</definedName>
@@ -12009,14 +12010,14 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E133"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v/>
       </c>
       <c r="B1" t="str">
-        <v/>
+        <v>اسنادات قطاع البنين</v>
       </c>
       <c r="C1" t="str">
         <v/>
@@ -12033,7 +12034,7 @@
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>اسنادات ابتدائي</v>
+        <v/>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -12064,67 +12065,67 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>المعلم</v>
+        <v/>
       </c>
       <c r="B4" t="str">
-        <v>المادة</v>
+        <v>اسنادات ابتدائي (بنين)</v>
       </c>
       <c r="C4" t="str">
-        <v>عدد حصص المعلم بالمدرسة</v>
+        <v/>
       </c>
       <c r="D4" t="str">
-        <v>الإسناد</v>
+        <v/>
       </c>
       <c r="E4" t="str">
-        <v>إجمالي نصاب المعلم</v>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>العفيفي عبد الجواد</v>
+        <v/>
       </c>
       <c r="B5" t="str">
-        <v>معلم صف أول</v>
+        <v/>
       </c>
       <c r="C5" t="str">
-        <v>24</v>
+        <v/>
       </c>
       <c r="D5" t="str">
-        <v>(٨) لغتي ص١+ (٤) اسلاميات ص١+ (٥) رياضيات ص١+ (٢) بدنية ص١+ (١) مهارات حياتية ص١ + (1) فنية ص١ + (3) علوم ص1</v>
+        <v/>
       </c>
       <c r="E5" t="str">
-        <v>24</v>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>محمود عبدالحسيب</v>
+        <v>المعلم</v>
       </c>
       <c r="B6" t="str">
-        <v>معلم صف أول</v>
+        <v>المادة</v>
       </c>
       <c r="C6" t="str">
-        <v>24</v>
+        <v>عدد حصص المعلم بالمدرسة</v>
       </c>
       <c r="D6" t="str">
-        <v>(٨) لغتي ص١+ (٤) اسلاميات ص١+ (٥) رياضيات ص١+ (٢) بدنية ص١+ (١) مهارات حياتية ص١ + (1) فنية ص١ + (3) علوم ص1</v>
+        <v>الإسناد</v>
       </c>
       <c r="E6" t="str">
-        <v>24</v>
+        <v>إجمالي نصاب المعلم</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>عبد العزيز يونس</v>
+        <v>العفيفي عبد الجواد</v>
       </c>
       <c r="B7" t="str">
-        <v>معلم صف ثاني</v>
+        <v>معلم صف أول</v>
       </c>
       <c r="C7" t="str">
         <v>24</v>
       </c>
       <c r="D7" t="str">
-        <v xml:space="preserve">(١٤) لغتي ص٢ فصلين + (١٠) اسلاميات ص٢ فصلين </v>
+        <v>(٨) لغتي ص١+ (٤) اسلاميات ص١+ (٥) رياضيات ص١+ (٢) بدنية ص١+ (١) مهارات حياتية ص١ + (1) فنية ص١ + (3) علوم ص1</v>
       </c>
       <c r="E7" t="str">
         <v>24</v>
@@ -12132,16 +12133,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>حسن عزالدين مبروك</v>
+        <v>محمود عبدالحسيب</v>
       </c>
       <c r="B8" t="str">
-        <v>معلم صف ثالث</v>
+        <v>معلم صف أول</v>
       </c>
       <c r="C8" t="str">
         <v>24</v>
       </c>
       <c r="D8" t="str">
-        <v>(١٤) لغتي ص٣ فصلين(2/4 ، 3/4) + (١٠) اسلاميات ص٣ فصلين +(٢) مهارات حياتية ص٣ فصلين</v>
+        <v>(٨) لغتي ص١+ (٤) اسلاميات ص١+ (٥) رياضيات ص١+ (٢) بدنية ص١+ (١) مهارات حياتية ص١ + (1) فنية ص١ + (3) علوم ص1</v>
       </c>
       <c r="E8" t="str">
         <v>24</v>
@@ -12149,16 +12150,16 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>سلمان حمد الفراج</v>
+        <v>عبد العزيز يونس</v>
       </c>
       <c r="B9" t="str">
-        <v>اسلاميات</v>
+        <v>معلم صف ثاني</v>
       </c>
       <c r="C9" t="str">
         <v>24</v>
       </c>
       <c r="D9" t="str">
-        <v>(١٢) اسلاميات ص٤ فصلين (2/4 ،3/4)+ (٨) اسلاميات ص٥+ (٤) اسلاميات ص٦ فصلين</v>
+        <v xml:space="preserve">(١٤) لغتي ص٢ فصلين + (١٠) اسلاميات ص٢ فصلين </v>
       </c>
       <c r="E9" t="str">
         <v>24</v>
@@ -12166,33 +12167,33 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>محمد الغباشي</v>
+        <v>حسن عزالدين مبروك</v>
       </c>
       <c r="B10" t="str">
-        <v>لغة عربية</v>
+        <v>معلم صف ثالث</v>
       </c>
       <c r="C10" t="str">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10" t="str">
-        <v>(٥) لغتي ص 4 فصل(2/4) + (١٠) لغتي ص٥ فصلين +(١٠) لغتي ص٦ فصلين</v>
+        <v>(١٤) لغتي ص٣ فصلين(2/4 ، 3/4) + (١٠) اسلاميات ص٣ فصلين +(٢) مهارات حياتية ص٣ فصلين</v>
       </c>
       <c r="E10" t="str">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>طارق عبدالظاهر</v>
+        <v>سلمان حمد الفراج</v>
       </c>
       <c r="B11" t="str">
-        <v>رياضيات</v>
+        <v>اسلاميات</v>
       </c>
       <c r="C11" t="str">
         <v>24</v>
       </c>
       <c r="D11" t="str">
-        <v>(18) رياضيات ص٤ +(6) رياضيات ص٥ فصل</v>
+        <v>(١٢) اسلاميات ص٤ فصلين (2/4 ،3/4)+ (٨) اسلاميات ص٥+ (٤) اسلاميات ص٦ فصلين</v>
       </c>
       <c r="E11" t="str">
         <v>24</v>
@@ -12200,24 +12201,24 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v xml:space="preserve">احمد سالم </v>
+        <v>محمد الغباشي</v>
       </c>
       <c r="B12" t="str">
-        <v>رياضيات</v>
+        <v>لغة عربية</v>
       </c>
       <c r="C12" t="str">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D12" t="str">
-        <v>(١٢) رياضيات ص٦ فصلين  + مسند (6) رياضيات ص5 فصل + (5) نشاط ص4 وص5 + (1) نشاط ص6 فصل</v>
+        <v>(٥) لغتي ص 4 فصل(2/4) + (١٠) لغتي ص٥ فصلين +(١٠) لغتي ص٦ فصلين</v>
       </c>
       <c r="E12" t="str">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v xml:space="preserve">عمرو محمد </v>
+        <v>طارق عبدالظاهر</v>
       </c>
       <c r="B13" t="str">
         <v>رياضيات</v>
@@ -12226,7 +12227,7 @@
         <v>24</v>
       </c>
       <c r="D13" t="str">
-        <v xml:space="preserve">(12) رياضيات ص٢ ب فصلين+(12) رياضيات ص٣ فصلين </v>
+        <v>(18) رياضيات ص٤ +(6) رياضيات ص٥ فصل</v>
       </c>
       <c r="E13" t="str">
         <v>24</v>
@@ -12234,16 +12235,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ربيع عوض</v>
+        <v xml:space="preserve">احمد سالم </v>
       </c>
       <c r="B14" t="str">
-        <v>لغة انجليزية</v>
+        <v>رياضيات</v>
       </c>
       <c r="C14" t="str">
         <v>24</v>
       </c>
       <c r="D14" t="str">
-        <v>(٦) E ص٥ + (٦) E ص٦ + (٩) E ص٤ + (2) انجليزي إثرائي ص6 + (1) نشاط ص6 فصل</v>
+        <v>(١٢) رياضيات ص٦ فصلين  + مسند (6) رياضيات ص5 فصل + (5) نشاط ص4 وص5 + (1) نشاط ص6 فصل</v>
       </c>
       <c r="E14" t="str">
         <v>24</v>
@@ -12251,16 +12252,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>محمد السيد</v>
+        <v xml:space="preserve">عمرو محمد </v>
       </c>
       <c r="B15" t="str">
-        <v>لغة انجليزية</v>
+        <v>رياضيات</v>
       </c>
       <c r="C15" t="str">
         <v>24</v>
       </c>
       <c r="D15" t="str">
-        <v xml:space="preserve"> (٦) E ص٣ + + (٤) E اثرائي ص3  + (٦) E اثرائي ص٤ + (2) E اثرائي ص٦+ (٤) E اثراىي ص٥ +(2) انجليزي اثرائي ص2 فصل</v>
+        <v xml:space="preserve">(12) رياضيات ص٢ ب فصلين+(12) رياضيات ص٣ فصلين </v>
       </c>
       <c r="E15" t="str">
         <v>24</v>
@@ -12268,7 +12269,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>احمد حسنين</v>
+        <v>ربيع عوض</v>
       </c>
       <c r="B16" t="str">
         <v>لغة انجليزية</v>
@@ -12277,7 +12278,7 @@
         <v>24</v>
       </c>
       <c r="D16" t="str">
-        <v>(6) E ص١+ (٤) E اثرائي ص١+ (٦) E ص٢ + (2) E اثرائي ص٢ فصل+ (4) ماث ص١ + (٢) ساينس ص١</v>
+        <v>(٦) E ص٥ + (٦) E ص٦ + (٩) E ص٤ + (2) انجليزي إثرائي ص6 + (1) نشاط ص6 فصل</v>
       </c>
       <c r="E16" t="str">
         <v>24</v>
@@ -12285,16 +12286,16 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v xml:space="preserve"> ايمن محمد </v>
+        <v>محمد السيد</v>
       </c>
       <c r="B17" t="str">
-        <v>علوم</v>
+        <v>لغة انجليزية</v>
       </c>
       <c r="C17" t="str">
         <v>24</v>
       </c>
       <c r="D17" t="str">
-        <v>(٦) علوم ص2 فصلين+ (8) علوم ص٣ فصلين+ (٨) علوم ص4 فصلين(1/4،2/4)+ (٢) بدنية ص5 فصل (2/5)</v>
+        <v xml:space="preserve"> (٦) E ص٣ + + (٤) E اثرائي ص3  + (٦) E اثرائي ص٤ + (2) E اثرائي ص٦+ (٤) E اثراىي ص٥ +(2) انجليزي اثرائي ص2 فصل</v>
       </c>
       <c r="E17" t="str">
         <v>24</v>
@@ -12302,16 +12303,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>مصطفى عبدالتواب</v>
+        <v>احمد حسنين</v>
       </c>
       <c r="B18" t="str">
-        <v>علوم</v>
+        <v>لغة انجليزية</v>
       </c>
       <c r="C18" t="str">
         <v>24</v>
       </c>
       <c r="D18" t="str">
-        <v>(٨) علوم ص٥  + (٨) علوم ص٦ + (٤) علوم ص٤ + (٤) اجتماعيات ص٦</v>
+        <v>(6) E ص١+ (٤) E اثرائي ص١+ (٦) E ص٢ + (2) E اثرائي ص٢ فصل+ (4) ماث ص١ + (٢) ساينس ص١</v>
       </c>
       <c r="E18" t="str">
         <v>24</v>
@@ -12319,16 +12320,16 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>محمد إبراهيم</v>
+        <v xml:space="preserve"> ايمن محمد </v>
       </c>
       <c r="B19" t="str">
-        <v>لغة عربية</v>
+        <v>علوم</v>
       </c>
       <c r="C19" t="str">
         <v>24</v>
       </c>
       <c r="D19" t="str">
-        <v>(١٠) لغتي ص٤ فصلين(1/4،3/4) + (٤) اسلاميات ص4 فصل(1/4) + (١٠) اجتماعيات ص٤ فصلين ص٥ فصلين</v>
+        <v>(٦) علوم ص2 فصلين+ (8) علوم ص٣ فصلين+ (٨) علوم ص4 فصلين(1/4،2/4)+ (٢) بدنية ص5 فصل (2/5)</v>
       </c>
       <c r="E19" t="str">
         <v>24</v>
@@ -12336,16 +12337,16 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>رامي يسن معروف</v>
+        <v>مصطفى عبدالتواب</v>
       </c>
       <c r="B20" t="str">
-        <v>فنية</v>
+        <v>علوم</v>
       </c>
       <c r="C20" t="str">
         <v>24</v>
       </c>
       <c r="D20" t="str">
-        <v>(٤) فنية ص٢+ (٤) فنية ص٣ + (٣) فنية ص٤ + (٢) فنية ص٥ + (٢) فنية ص٦ + (٩) مهارات حياتية ص٢، ص٤، ص٥، ص٦</v>
+        <v>(٨) علوم ص٥  + (٨) علوم ص٦ + (٤) علوم ص٤ + (٤) اجتماعيات ص٦</v>
       </c>
       <c r="E20" t="str">
         <v>24</v>
@@ -12353,16 +12354,16 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>محمود وحش</v>
+        <v>محمد إبراهيم</v>
       </c>
       <c r="B21" t="str">
-        <v>بدنية</v>
+        <v>لغة عربية</v>
       </c>
       <c r="C21" t="str">
         <v>24</v>
       </c>
       <c r="D21" t="str">
-        <v>(6) بدنية ص٣ + (٦) بدنية ص٤ + (6) بدنية ص٢  + (2) بدنية ص٥ +  (4) بدنية ص6</v>
+        <v>(١٠) لغتي ص٤ فصلين(1/4،3/4) + (٤) اسلاميات ص4 فصل(1/4) + (١٠) اجتماعيات ص٤ فصلين ص٥ فصلين</v>
       </c>
       <c r="E21" t="str">
         <v>24</v>
@@ -12370,32 +12371,66 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>آمير جلال</v>
+        <v>رامي يسن معروف</v>
       </c>
       <c r="B22" t="str">
-        <v>رقمية</v>
+        <v>فنية</v>
       </c>
       <c r="C22" t="str">
         <v>24</v>
       </c>
       <c r="D22" t="str">
-        <v xml:space="preserve">(2) رقمية ص١+ (٤) رقمية ص٢+ (٤) رقمية ص٣ + (٦) رقمية ص٤ + (٤) رقمية ص٥ + (٤) رقمية ص٦ </v>
+        <v>(٤) فنية ص٢+ (٤) فنية ص٣ + (٣) فنية ص٤ + (٢) فنية ص٥ + (٢) فنية ص٦ + (٩) مهارات حياتية ص٢، ص٤، ص٥، ص٦</v>
       </c>
       <c r="E22" t="str">
         <v>24</v>
       </c>
     </row>
-    <row r="23" xml:space="preserve">
+    <row r="23">
       <c r="A23" t="str">
+        <v>محمود وحش</v>
+      </c>
+      <c r="B23" t="str">
+        <v>بدنية</v>
+      </c>
+      <c r="C23" t="str">
+        <v>24</v>
+      </c>
+      <c r="D23" t="str">
+        <v>(6) بدنية ص٣ + (٦) بدنية ص٤ + (6) بدنية ص٢  + (2) بدنية ص٥ +  (4) بدنية ص6</v>
+      </c>
+      <c r="E23" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>آمير جلال</v>
+      </c>
+      <c r="B24" t="str">
+        <v>رقمية</v>
+      </c>
+      <c r="C24" t="str">
+        <v>24</v>
+      </c>
+      <c r="D24" t="str">
+        <v xml:space="preserve">(2) رقمية ص١+ (٤) رقمية ص٢+ (٤) رقمية ص٣ + (٦) رقمية ص٤ + (٤) رقمية ص٥ + (٤) رقمية ص٦ </v>
+      </c>
+      <c r="E24" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="A25" t="str">
         <v>إجمالي الحصص</v>
       </c>
-      <c r="B23" t="str">
+      <c r="B25" t="str">
         <v>396</v>
       </c>
-      <c r="C23" t="str">
+      <c r="C25" t="str">
         <v>433</v>
       </c>
-      <c r="D23" t="str" xml:space="preserve">
+      <c r="D25" t="str" xml:space="preserve">
         <v xml:space="preserve">اضافة عدد (٣٨) حصة اثرائي لغة انجليزية + (١٢) اثرائي رقمية صفوف أولية فيصبح مجموع الحصص الاثرائية (٥٠) حصة _x000d_
 تخفيض (١) حصة فنية الصف الاول باجمالي (٢) حصة_x000d_
 تخفيض (١) حصة بدنية الصف الاول باجمالي (٢) حصة_x000d_
@@ -12405,40 +12440,6 @@
 استبدال  (٣٢) حصة نشاط  مع الحصص الاثرائية _x000d_
 (٥٠) - (٣٢) = (١٨) حصة </v>
       </c>
-      <c r="E23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v/>
-      </c>
-      <c r="B24" t="str">
-        <v/>
-      </c>
-      <c r="C24" t="str">
-        <v/>
-      </c>
-      <c r="D24" t="str">
-        <v/>
-      </c>
-      <c r="E24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>اسنادات متوسط دار القلم الفصل الاول 1447</v>
-      </c>
-      <c r="B25" t="str">
-        <v/>
-      </c>
-      <c r="C25" t="str">
-        <v/>
-      </c>
-      <c r="D25" t="str">
-        <v/>
-      </c>
       <c r="E25" t="str">
         <v/>
       </c>
@@ -12462,135 +12463,135 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>المعلم</v>
+        <v/>
       </c>
       <c r="B27" t="str">
-        <v>المادة</v>
+        <v>اسنادات متوسط (بنين)</v>
       </c>
       <c r="C27" t="str">
-        <v>عدد حصص المعلم بالمدرسة</v>
+        <v/>
       </c>
       <c r="D27" t="str">
-        <v>الإسناد</v>
+        <v/>
       </c>
       <c r="E27" t="str">
-        <v>إجمالي نصاب المعلم</v>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>فواز المطيري</v>
+        <v/>
       </c>
       <c r="B28" t="str">
-        <v>اسلاميات</v>
+        <v/>
       </c>
       <c r="C28" t="str">
-        <v>25</v>
+        <v/>
       </c>
       <c r="D28" t="str">
-        <v xml:space="preserve"> (5) اسلاميات ص1 فصل 1/1 +(10) اسلاميات ص2 فصلين 2/1 - 2/2 + (10) اسلاميات ص 3 فصل 3/1 - 3/2 </v>
+        <v/>
       </c>
       <c r="E28" t="str">
-        <v>25</v>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>احمد صوفي</v>
+        <v>المعلم</v>
       </c>
       <c r="B29" t="str">
-        <v>لغة عربية</v>
+        <v>المادة</v>
       </c>
       <c r="C29" t="str">
-        <v>26</v>
+        <v>عدد حصص المعلم بالمدرسة</v>
       </c>
       <c r="D29" t="str">
-        <v xml:space="preserve"> (15) لغتي ص1 متوسط   +  (٥) اسلاميات ص2  فصل 2/3  +(6) تفكير ناقد متوسط ص٣</v>
+        <v>الإسناد</v>
       </c>
       <c r="E29" t="str">
-        <v>26</v>
+        <v>إجمالي نصاب المعلم</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>محمد سمير</v>
+        <v>فواز المطيري</v>
       </c>
       <c r="B30" t="str">
-        <v>لغة عربية</v>
+        <v>اسلاميات</v>
       </c>
       <c r="C30" t="str">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D30" t="str">
-        <v xml:space="preserve">(15) لغتي ص2 م + (12 ) لغتي ص 3 </v>
+        <v xml:space="preserve"> (5) اسلاميات ص1 فصل 1/1 +(10) اسلاميات ص2 فصلين 2/1 - 2/2 + (10) اسلاميات ص 3 فصل 3/1 - 3/2 </v>
       </c>
       <c r="E30" t="str">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ماهر الحربي</v>
+        <v>احمد صوفي</v>
       </c>
       <c r="B31" t="str">
-        <v>رياضيات</v>
+        <v>لغة عربية</v>
       </c>
       <c r="C31" t="str">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D31" t="str">
-        <v>(18) رياضيات ص١+ (6) رياضيات ص2م فصل 2/3</v>
+        <v xml:space="preserve"> (15) لغتي ص1 متوسط   +  (٥) اسلاميات ص2  فصل 2/3  +(6) تفكير ناقد متوسط ص٣</v>
       </c>
       <c r="E31" t="str">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>حسن السيد</v>
+        <v>محمد سمير</v>
       </c>
       <c r="B32" t="str">
-        <v>رياضيات</v>
+        <v>لغة عربية</v>
       </c>
       <c r="C32" t="str">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D32" t="str">
-        <v>(18) رياضيات ص3م  + (6) رياضيات ص2م فصل 2/2 - 2/3</v>
+        <v xml:space="preserve">(15) لغتي ص2 م + (12 ) لغتي ص 3 </v>
       </c>
       <c r="E32" t="str">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v xml:space="preserve">سلمان الصادق </v>
+        <v>ماهر الحربي</v>
       </c>
       <c r="B33" t="str">
-        <v>لغة انجليزية</v>
+        <v>رياضيات</v>
       </c>
       <c r="C33" t="str">
         <v>24</v>
       </c>
       <c r="D33" t="str">
-        <v xml:space="preserve">(12) انجليزي ص٢متوسط +(12) انجليزي ص٣ متوسط  </v>
+        <v>(18) رياضيات ص١+ (6) رياضيات ص2م فصل 2/3</v>
       </c>
       <c r="E33" t="str">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>مصطفى فتحي</v>
+        <v>حسن السيد</v>
       </c>
       <c r="B34" t="str">
-        <v>لغة انجليزية</v>
+        <v>رياضيات</v>
       </c>
       <c r="C34" t="str">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D34" t="str">
-        <v xml:space="preserve"> (١٢) انجليزي ص١ متوسط + مكمل (١٢) حصة بالثانوي </v>
+        <v>(18) رياضيات ص3م  + (6) رياضيات ص2م فصل 2/2 - 2/3</v>
       </c>
       <c r="E34" t="str">
         <v>24</v>
@@ -12598,16 +12599,16 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>فارس الجندي</v>
+        <v xml:space="preserve">سلمان الصادق </v>
       </c>
       <c r="B35" t="str">
-        <v>علوم</v>
+        <v>لغة انجليزية</v>
       </c>
       <c r="C35" t="str">
         <v>24</v>
       </c>
       <c r="D35" t="str">
-        <v xml:space="preserve">(12) علوم ص١ +(12) علوم ص٢ </v>
+        <v xml:space="preserve">(12) انجليزي ص٢متوسط +(12) انجليزي ص٣ متوسط  </v>
       </c>
       <c r="E35" t="str">
         <v>24</v>
@@ -12615,33 +12616,33 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v xml:space="preserve">محمد العشماوي </v>
+        <v>مصطفى فتحي</v>
       </c>
       <c r="B36" t="str">
-        <v>علوم</v>
+        <v>لغة انجليزية</v>
       </c>
       <c r="C36" t="str">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D36" t="str">
-        <v>(12) علوم ص٣ +(10) اسلاميات ص1 فصل 1/2 - 1/3 + ( 5 ) اسلاميات  صف 3 فصل 3/3</v>
+        <v xml:space="preserve"> (١٢) انجليزي ص١ متوسط + مكمل (١٢) حصة بالثانوي </v>
       </c>
       <c r="E36" t="str">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>عبدالعزيز الربيعان</v>
+        <v>فارس الجندي</v>
       </c>
       <c r="B37" t="str">
-        <v>اجتماعيات</v>
+        <v>علوم</v>
       </c>
       <c r="C37" t="str">
         <v>24</v>
       </c>
       <c r="D37" t="str">
-        <v xml:space="preserve">(24) اجتماعيات (9) ص١ + (9 ) ص٢ +( 6 ) ص٣ متوسط   </v>
+        <v xml:space="preserve">(12) علوم ص١ +(12) علوم ص٢ </v>
       </c>
       <c r="E37" t="str">
         <v>24</v>
@@ -12649,16 +12650,16 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>محمود صابر</v>
+        <v xml:space="preserve">محمد العشماوي </v>
       </c>
       <c r="B38" t="str">
-        <v>فنية</v>
+        <v>علوم</v>
       </c>
       <c r="C38" t="str">
         <v>27</v>
       </c>
       <c r="D38" t="str">
-        <v xml:space="preserve">(18) فنية ص١ ص٢ ص٣ + (9) حياتية ص١ + ص2 + ص3 فصل </v>
+        <v>(12) علوم ص٣ +(10) اسلاميات ص1 فصل 1/2 - 1/3 + ( 5 ) اسلاميات  صف 3 فصل 3/3</v>
       </c>
       <c r="E38" t="str">
         <v>27</v>
@@ -12666,50 +12667,50 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>حسين عويضة (مكمل مكرر من الثانوي)</v>
+        <v>عبدالعزيز الربيعان</v>
       </c>
       <c r="B39" t="str">
-        <v>بدنية</v>
+        <v>اجتماعيات</v>
       </c>
       <c r="C39" t="str">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D39" t="str">
-        <v>( 6) بدنية ص2 متوسط +  (6) بدنية ص٣ متوسط + مكمل (١٣) حصة بالثانوي</v>
+        <v xml:space="preserve">(24) اجتماعيات (9) ص١ + (9 ) ص٢ +( 6 ) ص٣ متوسط   </v>
       </c>
       <c r="E39" t="str">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>محمد عبد الله (مكمل مكرر من الثانوي)</v>
+        <v>محمود صابر</v>
       </c>
       <c r="B40" t="str">
-        <v>رقمية</v>
+        <v>فنية</v>
       </c>
       <c r="C40" t="str">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D40" t="str">
-        <v>(6) رقمية  ص٣ متوسط+ (2) رقمية  ص٢ متوسط فصل 3 + مكمل (١٨) حصة بالثانوي</v>
+        <v xml:space="preserve">(18) فنية ص١ ص٢ ص٣ + (9) حياتية ص١ + ص2 + ص3 فصل </v>
       </c>
       <c r="E40" t="str">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v xml:space="preserve">محمود جمعه </v>
+        <v>حسين عويضة (مكمل مكرر من الثانوي)</v>
       </c>
       <c r="B41" t="str">
-        <v>رقمية</v>
+        <v>بدنية</v>
       </c>
       <c r="C41" t="str">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D41" t="str">
-        <v>(٦) رقمية  ص١متوسط +(4) رقمية  ص٢ متوسط فصل 1  + فصل 2  + ( 6) بدنية ص1 متوسط + (3) نشاط ص1 + (3) نشاط ص 3 + (3) نشاط ص2</v>
+        <v>( 6) بدنية ص2 متوسط +  (6) بدنية ص٣ متوسط + مكمل (١٣) حصة بالثانوي</v>
       </c>
       <c r="E41" t="str">
         <v>25</v>
@@ -12717,53 +12718,53 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v/>
+        <v>محمد عبد الله (مكمل مكرر من الثانوي)</v>
       </c>
       <c r="B42" t="str">
-        <v/>
+        <v>رقمية</v>
       </c>
       <c r="C42" t="str">
-        <v>315</v>
+        <v>8</v>
       </c>
       <c r="D42" t="str">
-        <v/>
+        <v>(6) رقمية  ص٣ متوسط+ (2) رقمية  ص٢ متوسط فصل 3 + مكمل (١٨) حصة بالثانوي</v>
       </c>
       <c r="E42" t="str">
-        <v>358</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v/>
+        <v xml:space="preserve">محمود جمعه </v>
       </c>
       <c r="B43" t="str">
-        <v/>
+        <v>رقمية</v>
       </c>
       <c r="C43" t="str">
-        <v/>
+        <v>25</v>
       </c>
       <c r="D43" t="str">
-        <v/>
+        <v>(٦) رقمية  ص١متوسط +(4) رقمية  ص٢ متوسط فصل 1  + فصل 2  + ( 6) بدنية ص1 متوسط + (3) نشاط ص1 + (3) نشاط ص 3 + (3) نشاط ص2</v>
       </c>
       <c r="E43" t="str">
-        <v/>
+        <v>25</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>اسنادات ثانوية دار القلم الفصل الدراسي الأول 1447</v>
+        <v/>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v/>
+        <v>315</v>
       </c>
       <c r="D44" t="str">
         <v/>
       </c>
       <c r="E44" t="str">
-        <v/>
+        <v>358</v>
       </c>
     </row>
     <row r="45">
@@ -12785,58 +12786,58 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>المعلم</v>
+        <v/>
       </c>
       <c r="B46" t="str">
-        <v>المادة</v>
+        <v>اسنادات ثانوي (بنين)</v>
       </c>
       <c r="C46" t="str">
-        <v>عدد حصص المعلم بالمدرسة</v>
+        <v/>
       </c>
       <c r="D46" t="str">
-        <v>الإسناد</v>
+        <v/>
       </c>
       <c r="E46" t="str">
-        <v>عدد حصص المعلم بالمدرسة</v>
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>احمد نصر</v>
+        <v/>
       </c>
       <c r="B47" t="str">
-        <v xml:space="preserve">لغة عربية </v>
+        <v/>
       </c>
       <c r="C47" t="str">
-        <v>24</v>
+        <v/>
       </c>
       <c r="D47" t="str">
-        <v>20 كفايات 1ث من 6:2 +4 كفايات 2ث 7</v>
+        <v/>
       </c>
       <c r="E47" t="str">
-        <v>24</v>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v xml:space="preserve">هشام رسمي </v>
+        <v>المعلم</v>
       </c>
       <c r="B48" t="str">
-        <v xml:space="preserve">لغة عربية </v>
+        <v>المادة</v>
       </c>
       <c r="C48" t="str">
-        <v>27</v>
+        <v>عدد حصص المعلم بالمدرسة</v>
       </c>
       <c r="D48" t="str">
-        <v xml:space="preserve">24 حصة كفايات  2ث 6فصول من 6:1+ 3 حصص 2-ث نون </v>
+        <v>الإسناد</v>
       </c>
       <c r="E48" t="str">
-        <v>27</v>
+        <v>عدد حصص المعلم بالمدرسة</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v xml:space="preserve">حسن الخطيب </v>
+        <v>احمد نصر</v>
       </c>
       <c r="B49" t="str">
         <v xml:space="preserve">لغة عربية </v>
@@ -12845,7 +12846,7 @@
         <v>24</v>
       </c>
       <c r="D49" t="str">
-        <v>14 مهارا ت بحث 3 ث كامل + 6 كفايات 1ث نون  +4 كفايات 1ث 1</v>
+        <v>20 كفايات 1ث من 6:2 +4 كفايات 2ث 7</v>
       </c>
       <c r="E49" t="str">
         <v>24</v>
@@ -12853,135 +12854,135 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v xml:space="preserve">عبد العزيز الربيعان </v>
+        <v xml:space="preserve">هشام رسمي </v>
       </c>
       <c r="B50" t="str">
         <v xml:space="preserve">لغة عربية </v>
       </c>
       <c r="C50" t="str">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D50" t="str">
-        <v>21 تاريخ 2ث كامل+2 تاريخ 2ث نون +3 تفسير 1ث2 نون</v>
+        <v xml:space="preserve">24 حصة كفايات  2ث 6فصول من 6:1+ 3 حصص 2-ث نون </v>
       </c>
       <c r="E50" t="str">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>خالد المطيري</v>
+        <v xml:space="preserve">حسن الخطيب </v>
       </c>
       <c r="B51" t="str">
-        <v xml:space="preserve">اسلاميات </v>
+        <v xml:space="preserve">لغة عربية </v>
       </c>
       <c r="C51" t="str">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D51" t="str">
-        <v xml:space="preserve">24 تفسير وقران 1ث كامل + 3 تفسير 1ث1 نون </v>
+        <v>14 مهارا ت بحث 3 ث كامل + 6 كفايات 1ث نون  +4 كفايات 1ث 1</v>
       </c>
       <c r="E51" t="str">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v xml:space="preserve">حسام السيد </v>
+        <v xml:space="preserve">عبد العزيز الربيعان </v>
       </c>
       <c r="B52" t="str">
-        <v xml:space="preserve">رياضيات </v>
+        <v xml:space="preserve">لغة عربية </v>
       </c>
       <c r="C52" t="str">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D52" t="str">
-        <v xml:space="preserve">20 صف2ث 4 فصول 4:1+4 نون صف2ث + 4 صف3ث1 </v>
+        <v>21 تاريخ 2ث كامل+2 تاريخ 2ث نون +3 تفسير 1ث2 نون</v>
       </c>
       <c r="E52" t="str">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v xml:space="preserve">محمد سليم </v>
+        <v>خالد المطيري</v>
       </c>
       <c r="B53" t="str">
-        <v xml:space="preserve">رياضيات </v>
+        <v xml:space="preserve">اسلاميات </v>
       </c>
       <c r="C53" t="str">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D53" t="str">
-        <v>20صف 3ث من 6:2 +8 حصص 1 ث نون 1-2</v>
+        <v xml:space="preserve">24 تفسير وقران 1ث كامل + 3 تفسير 1ث1 نون </v>
       </c>
       <c r="E53" t="str">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v xml:space="preserve">وليد الصدة </v>
+        <v xml:space="preserve">حسام السيد </v>
       </c>
       <c r="B54" t="str">
         <v xml:space="preserve">رياضيات </v>
       </c>
       <c r="C54" t="str">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D54" t="str">
-        <v xml:space="preserve">20 1ث  4 فصول من4:1+ 4 حصص 3ث7 </v>
+        <v xml:space="preserve">20 صف2ث 4 فصول 4:1+4 نون صف2ث + 4 صف3ث1 </v>
       </c>
       <c r="E54" t="str">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>وسيم عبد ربه</v>
+        <v xml:space="preserve">محمد سليم </v>
       </c>
       <c r="B55" t="str">
         <v xml:space="preserve">رياضيات </v>
       </c>
       <c r="C55" t="str">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D55" t="str">
-        <v>10 صف 1ث  6:5+ 15 صف 2ث من 7:5</v>
+        <v>20صف 3ث من 6:2 +8 حصص 1 ث نون 1-2</v>
       </c>
       <c r="E55" t="str">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v xml:space="preserve">أحمد طاهر بهيدي </v>
+        <v xml:space="preserve">وليد الصدة </v>
       </c>
       <c r="B56" t="str">
-        <v xml:space="preserve">كيمياء </v>
+        <v xml:space="preserve">رياضيات </v>
       </c>
       <c r="C56" t="str">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D56" t="str">
-        <v>18 صف 1ث كامل + 6 حصص 1 ث نون 2:1 + 3 علم أرض 3ث7</v>
+        <v xml:space="preserve">20 1ث  4 فصول من4:1+ 4 حصص 3ث7 </v>
       </c>
       <c r="E56" t="str">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v xml:space="preserve">أحمد محمد مصباح </v>
+        <v>وسيم عبد ربه</v>
       </c>
       <c r="B57" t="str">
-        <v xml:space="preserve">كيمياء </v>
+        <v xml:space="preserve">رياضيات </v>
       </c>
       <c r="C57" t="str">
         <v>25</v>
       </c>
       <c r="D57" t="str">
-        <v>25 حصة صف2 ث من 5:1</v>
+        <v>10 صف 1ث  6:5+ 15 صف 2ث من 7:5</v>
       </c>
       <c r="E57" t="str">
         <v>25</v>
@@ -12989,33 +12990,33 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>محمد متولي</v>
+        <v xml:space="preserve">أحمد طاهر بهيدي </v>
       </c>
       <c r="B58" t="str">
         <v xml:space="preserve">كيمياء </v>
       </c>
       <c r="C58" t="str">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D58" t="str">
-        <v>21 صف 3 ث كامل + 5 حصص 2 ث نون</v>
+        <v>18 صف 1ث كامل + 6 حصص 1 ث نون 2:1 + 3 علم أرض 3ث7</v>
       </c>
       <c r="E58" t="str">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>حسن جوده</v>
+        <v xml:space="preserve">أحمد محمد مصباح </v>
       </c>
       <c r="B59" t="str">
-        <v>كيمياء - فيزياء</v>
+        <v xml:space="preserve">كيمياء </v>
       </c>
       <c r="C59" t="str">
         <v>25</v>
       </c>
       <c r="D59" t="str">
-        <v>10كيمياء  صف 2ث 7:6+15فيزياء  صف 3ث 3:1</v>
+        <v>25 حصة صف2 ث من 5:1</v>
       </c>
       <c r="E59" t="str">
         <v>25</v>
@@ -13023,75 +13024,75 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>فريج السعيد</v>
+        <v>محمد متولي</v>
       </c>
       <c r="B60" t="str">
-        <v xml:space="preserve">فيزياء </v>
+        <v xml:space="preserve">كيمياء </v>
       </c>
       <c r="C60" t="str">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D60" t="str">
-        <v xml:space="preserve"> 20صف 3ث 7:4 + 4 حصص 2 ث7</v>
+        <v>21 صف 3 ث كامل + 5 حصص 2 ث نون</v>
       </c>
       <c r="E60" t="str">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v xml:space="preserve">سلمان محمد </v>
+        <v>حسن جوده</v>
       </c>
       <c r="B61" t="str">
-        <v xml:space="preserve">فيزياء </v>
+        <v>كيمياء - فيزياء</v>
       </c>
       <c r="C61" t="str">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D61" t="str">
-        <v xml:space="preserve">24 حصة صف2 ث 6 فصول 6:1 + 4 حصص 2ث نون </v>
+        <v>10كيمياء  صف 2ث 7:6+15فيزياء  صف 3ث 3:1</v>
       </c>
       <c r="E61" t="str">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v xml:space="preserve">محمد عبد المنعم </v>
+        <v>فريج السعيد</v>
       </c>
       <c r="B62" t="str">
-        <v xml:space="preserve">أحياء </v>
+        <v xml:space="preserve">فيزياء </v>
       </c>
       <c r="C62" t="str">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D62" t="str">
-        <v>18 صف 1ث كامل + 3 علم ارض ص ثالث6 +6 حصص 1 ث نون 1و2</v>
+        <v xml:space="preserve"> 20صف 3ث 7:4 + 4 حصص 2 ث7</v>
       </c>
       <c r="E62" t="str">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>حسن ابوغنيمة</v>
+        <v xml:space="preserve">سلمان محمد </v>
       </c>
       <c r="B63" t="str">
-        <v xml:space="preserve">أحياء </v>
+        <v xml:space="preserve">فيزياء </v>
       </c>
       <c r="C63" t="str">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D63" t="str">
-        <v>20 حصة 2ث 4:1+4أحياء  2ث نون+ مسند له كلاسيرا</v>
+        <v xml:space="preserve">24 حصة صف2 ث 6 فصول 6:1 + 4 حصص 2ث نون </v>
       </c>
       <c r="E63" t="str">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>محمد علي</v>
+        <v xml:space="preserve">محمد عبد المنعم </v>
       </c>
       <c r="B64" t="str">
         <v xml:space="preserve">أحياء </v>
@@ -13100,7 +13101,7 @@
         <v>27</v>
       </c>
       <c r="D64" t="str">
-        <v>15 علم أرض 3ث من 5:3 + 12 أحياءص2ث 7:5</v>
+        <v>18 صف 1ث كامل + 3 علم ارض ص ثالث6 +6 حصص 1 ث نون 1و2</v>
       </c>
       <c r="E64" t="str">
         <v>27</v>
@@ -13108,84 +13109,84 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v xml:space="preserve">مصطفى محمد </v>
+        <v>حسن ابوغنيمة</v>
       </c>
       <c r="B65" t="str">
-        <v xml:space="preserve">لغة انجليزية </v>
+        <v xml:space="preserve">أحياء </v>
       </c>
       <c r="C65" t="str">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D65" t="str">
-        <v>24حصة اث كامل + 2 حصة 1ث نون 1</v>
+        <v>20 حصة 2ث 4:1+4أحياء  2ث نون+ مسند له كلاسيرا</v>
       </c>
       <c r="E65" t="str">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v xml:space="preserve">عبد الرحمن شطا </v>
+        <v>محمد علي</v>
       </c>
       <c r="B66" t="str">
-        <v xml:space="preserve">لغة انجليزية </v>
+        <v xml:space="preserve">أحياء </v>
       </c>
       <c r="C66" t="str">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D66" t="str">
-        <v>20حصة 2 ث من5:1+ 4 حصص 3ث1+ 1 حصة نون 2ث</v>
+        <v>15 علم أرض 3ث من 5:3 + 12 أحياءص2ث 7:5</v>
       </c>
       <c r="E66" t="str">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v xml:space="preserve">مصطفى فتحي (مكرر مكمل من المتوسط) </v>
+        <v xml:space="preserve">مصطفى محمد </v>
       </c>
       <c r="B67" t="str">
         <v xml:space="preserve">لغة انجليزية </v>
       </c>
       <c r="C67" t="str">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D67" t="str">
-        <v>8 حصص 2 ث 6 و7 + 4 تفكير ناقد صف 1ث نون 1و2 + مكمل (١٢) حصة بالمتوسط</v>
+        <v>24حصة اث كامل + 2 حصة 1ث نون 1</v>
       </c>
       <c r="E67" t="str">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>إبراهيم شبكة</v>
+        <v xml:space="preserve">عبد الرحمن شطا </v>
       </c>
       <c r="B68" t="str">
         <v xml:space="preserve">لغة انجليزية </v>
       </c>
       <c r="C68" t="str">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D68" t="str">
-        <v>24 حصة صف 3ث 7:2</v>
+        <v>20حصة 2 ث من5:1+ 4 حصص 3ث1+ 1 حصة نون 2ث</v>
       </c>
       <c r="E68" t="str">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>احمد توفيق</v>
+        <v xml:space="preserve">مصطفى فتحي (مكرر مكمل من المتوسط) </v>
       </c>
       <c r="B69" t="str">
-        <v>تقنية -حاسب</v>
+        <v xml:space="preserve">لغة انجليزية </v>
       </c>
       <c r="C69" t="str">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D69" t="str">
-        <v>20 حصة مجال صف 3 ث 5:1+ 4 حصص 1ث نون تقنية 1و2</v>
+        <v>8 حصص 2 ث 6 و7 + 4 تفكير ناقد صف 1ث نون 1و2 + مكمل (١٢) حصة بالمتوسط</v>
       </c>
       <c r="E69" t="str">
         <v>24</v>
@@ -13193,16 +13194,16 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v xml:space="preserve">محمد مدحت </v>
+        <v>إبراهيم شبكة</v>
       </c>
       <c r="B70" t="str">
-        <v>تقنية -حاسب</v>
+        <v xml:space="preserve">لغة انجليزية </v>
       </c>
       <c r="C70" t="str">
         <v>24</v>
       </c>
       <c r="D70" t="str">
-        <v xml:space="preserve">18 حصة 1ث كامل  + 6تفكير ناقد 1ث </v>
+        <v>24 حصة صف 3ث 7:2</v>
       </c>
       <c r="E70" t="str">
         <v>24</v>
@@ -13210,83 +13211,117 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v xml:space="preserve">محمد صلاح </v>
+        <v>احمد توفيق</v>
       </c>
       <c r="B71" t="str">
-        <v xml:space="preserve">بدنية </v>
+        <v>تقنية -حاسب</v>
       </c>
       <c r="C71" t="str">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D71" t="str">
-        <v>12حصة 1ث كامل+12بدنية 3ث من  4:1 + 4 صف اول نون 1و2</v>
+        <v>20 حصة مجال صف 3 ث 5:1+ 4 حصص 1ث نون تقنية 1و2</v>
       </c>
       <c r="E71" t="str">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v xml:space="preserve">حسين عويضة </v>
+        <v xml:space="preserve">محمد مدحت </v>
       </c>
       <c r="B72" t="str">
-        <v xml:space="preserve">بدنية </v>
+        <v>تقنية -حاسب</v>
       </c>
       <c r="C72" t="str">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D72" t="str">
-        <v>9بدنية 3ث 7:5 + 8 مجال اختياري 3ث6 (م بالمتوسط بعد الفسحة) + مكمل (١٢) حصة بالمتوسط</v>
+        <v xml:space="preserve">18 حصة 1ث كامل  + 6تفكير ناقد 1ث </v>
       </c>
       <c r="E72" t="str">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v xml:space="preserve">عيد العتيبي + (م .اداري)   </v>
+        <v xml:space="preserve">محمد صلاح </v>
       </c>
       <c r="B73" t="str">
-        <v xml:space="preserve">علم نفس </v>
+        <v xml:space="preserve">بدنية </v>
       </c>
       <c r="C73" t="str">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D73" t="str">
-        <v xml:space="preserve"> 6 تفكير ناقد 1ث+ 7 نشاط 2ث + مكمل مراقب دور</v>
+        <v>12حصة 1ث كامل+12بدنية 3ث من  4:1 + 4 صف اول نون 1و2</v>
       </c>
       <c r="E73" t="str">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
+        <v xml:space="preserve">حسين عويضة </v>
+      </c>
+      <c r="B74" t="str">
+        <v xml:space="preserve">بدنية </v>
+      </c>
+      <c r="C74" t="str">
+        <v>13</v>
+      </c>
+      <c r="D74" t="str">
+        <v>9بدنية 3ث 7:5 + 8 مجال اختياري 3ث6 (م بالمتوسط بعد الفسحة) + مكمل (١٢) حصة بالمتوسط</v>
+      </c>
+      <c r="E74" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v xml:space="preserve">عيد العتيبي + (م .اداري)   </v>
+      </c>
+      <c r="B75" t="str">
+        <v xml:space="preserve">علم نفس </v>
+      </c>
+      <c r="C75" t="str">
+        <v>13</v>
+      </c>
+      <c r="D75" t="str">
+        <v xml:space="preserve"> 6 تفكير ناقد 1ث+ 7 نشاط 2ث + مكمل مراقب دور</v>
+      </c>
+      <c r="E75" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
         <v>محمد عبد الله</v>
       </c>
-      <c r="B74" t="str">
+      <c r="B76" t="str">
         <v>تقنية -حاسب</v>
       </c>
-      <c r="C74" t="str">
+      <c r="C76" t="str">
         <v>18</v>
       </c>
-      <c r="D74" t="str">
+      <c r="D76" t="str">
         <v>14 تقنية 3ث كامل + 4 مجال صف 3 ث 7+ مكمل (٨) حصص بالمتوسط</v>
       </c>
-      <c r="E74" t="str">
+      <c r="E76" t="str">
         <v>26</v>
       </c>
     </row>
-    <row r="75" xml:space="preserve">
-      <c r="A75" t="str">
+    <row r="77" xml:space="preserve">
+      <c r="A77" t="str">
         <v>إجمالي الحصص</v>
       </c>
-      <c r="B75" t="str">
-        <v/>
-      </c>
-      <c r="C75" t="str">
-        <v/>
-      </c>
-      <c r="D75" t="str" xml:space="preserve">
+      <c r="B77" t="str">
+        <v/>
+      </c>
+      <c r="C77" t="str">
+        <v/>
+      </c>
+      <c r="D77" t="str" xml:space="preserve">
         <v xml:space="preserve">تخفيض حصة من اللغة الإنجليزية أول ثانوي_x000d_
 تخفيض حصة من اللغة الإنجليزيةوثان _x000d_
 تخفيض حصة تفكير ناقد أول ثانوي _x000d_
@@ -13295,18 +13330,965 @@
 تخفيض حصة مجال صف ثالث ثانوي _x000d_
 عليه خروج جميع طلاب المدرسة بعد الحصة السادسة يوميا 11:50( بواقع تخفيض حصتين من كل فصل ) </v>
       </c>
-      <c r="E75" t="str">
+      <c r="E77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v/>
+      </c>
+      <c r="B78" t="str">
+        <v/>
+      </c>
+      <c r="C78" t="str">
+        <v/>
+      </c>
+      <c r="D78" t="str">
+        <v/>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v/>
+      </c>
+      <c r="B79" t="str">
+        <v>========================================</v>
+      </c>
+      <c r="C79" t="str">
+        <v/>
+      </c>
+      <c r="D79" t="str">
+        <v/>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v/>
+      </c>
+      <c r="B80" t="str">
+        <v>اسنادات قطاع البنات</v>
+      </c>
+      <c r="C80" t="str">
+        <v/>
+      </c>
+      <c r="D80" t="str">
+        <v/>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v/>
+      </c>
+      <c r="B81" t="str">
+        <v/>
+      </c>
+      <c r="C81" t="str">
+        <v/>
+      </c>
+      <c r="D81" t="str">
+        <v/>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v/>
+      </c>
+      <c r="B82" t="str">
+        <v>اسنادات ابتدائي (بنات)</v>
+      </c>
+      <c r="C82" t="str">
+        <v/>
+      </c>
+      <c r="D82" t="str">
+        <v/>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>المعلم</v>
+      </c>
+      <c r="B83" t="str">
+        <v>المادة</v>
+      </c>
+      <c r="C83" t="str">
+        <v xml:space="preserve">عدد حصص المعلم بالمرحلة </v>
+      </c>
+      <c r="D83" t="str">
+        <v>ملاحظات</v>
+      </c>
+      <c r="E83" t="str">
+        <v>إجمالي نصاب المعلم بعد الاكمال</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v/>
+      </c>
+      <c r="B84" t="str">
+        <v/>
+      </c>
+      <c r="C84" t="str">
+        <v/>
+      </c>
+      <c r="D84" t="str">
+        <v/>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v xml:space="preserve">نورا مجدي </v>
+      </c>
+      <c r="B85" t="str">
+        <v>انجليزي</v>
+      </c>
+      <c r="C85">
+        <v>24</v>
+      </c>
+      <c r="D85" t="str">
+        <v>(3) انجليزي وزاري ص1 ( 2) انجليزي اثرائي ص1 (1) ماث ص1 ( 1) ساينس ص1 ( 3) انجليزي وزاري ص2 (2) انجليزي اثرائي ص2 (6) انجليزي وزاري ص3 (4)انجليزي اثرائي ص3 (2) نشاط ص5</v>
+      </c>
+      <c r="E85">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v xml:space="preserve">سارة المخلفي </v>
+      </c>
+      <c r="B86" t="str">
+        <v>إسلامية</v>
+      </c>
+      <c r="C86">
+        <v>24</v>
+      </c>
+      <c r="D86" t="str">
+        <v>(10)اسلاميةص3(5)اسلاميةص4(5)إسلامية ص5(2)اجتماعيات ص5(2)نشاط ص4 + منسقة تطوع ابتدائي ومتوسط</v>
+      </c>
+      <c r="E86">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>نوير الشمري ( مكرر مكمل من الثانوي)</v>
+      </c>
+      <c r="B87" t="str">
+        <v>حاسب</v>
+      </c>
+      <c r="C87">
+        <v>8</v>
+      </c>
+      <c r="D87" t="str">
+        <v>(2) رقمية ص2 (2)رقمية ص4(2)رقمية ص5(2) رقمية ص6 + مسند (٦) حصص بالمتوسط + (10) حصة بالثانوي</v>
+      </c>
+      <c r="E87">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>نهال الشبرمي ( مكرر مكمل من المتوسط)</v>
+      </c>
+      <c r="B88" t="str">
+        <v>إسلامية</v>
+      </c>
+      <c r="C88">
+        <v>7</v>
+      </c>
+      <c r="D88" t="str">
+        <v>(2) بدنية ص6 (5) إسلامية ص6 + مسند (13) حصة بالمتوسط + (4) رقمية kg + منسقة الصيانة والمشتريات</v>
+      </c>
+      <c r="E88">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v xml:space="preserve">نوضا المطيري </v>
+      </c>
+      <c r="B89" t="str">
+        <v>رياضيات</v>
+      </c>
+      <c r="C89">
+        <v>24</v>
+      </c>
+      <c r="D89" t="str">
+        <v>(4)رياضيات ص1(3) علوم ص1 (3) علوم ص2 (6) رياضيات ص4 (2)اجتماعايت ص4 (1) اسرية ص4(1) نشاط ص3 فصل(4) رقمية ص3</v>
+      </c>
+      <c r="E89">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>الجوهرة المخلفي  ( مكرر مكمل من المتوسط)</v>
+      </c>
+      <c r="B90" t="str">
+        <v>لغة عربية</v>
+      </c>
+      <c r="C90">
+        <v>7</v>
+      </c>
+      <c r="D90" t="str">
+        <v>(5) لغتي ص6 (2) اجتماعيات ص6 + (17) حصة بالمتوسط + منسقة اختبارات مركزية</v>
+      </c>
+      <c r="E90">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>حنان العنزي (مكرر مكمل من متوسط )</v>
+      </c>
+      <c r="B91" t="str">
+        <v>انجليزي</v>
+      </c>
+      <c r="C91">
+        <v>3</v>
+      </c>
+      <c r="D91" t="str">
+        <v>(3) بدنية ص1 + مسند لها ( 11 ) متوسط + (11) ثانوي + منسقة اختبارات steep</v>
+      </c>
+      <c r="E91">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>أشواق العنزي</v>
+      </c>
+      <c r="B92" t="str">
+        <v xml:space="preserve"> لغة عربية</v>
+      </c>
+      <c r="C92">
+        <v>25</v>
+      </c>
+      <c r="D92" t="str">
+        <v>(8)لغتي ص1 (7)لغتي ص2 (5) إسلامية ص1(5) إسلامية ص2</v>
+      </c>
+      <c r="E92">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>ناهد بعزقي</v>
+      </c>
+      <c r="B93" t="str">
+        <v xml:space="preserve"> لغة عربية</v>
+      </c>
+      <c r="C93">
+        <v>24</v>
+      </c>
+      <c r="D93" t="str">
+        <v>(12) لغتي ص3 (5)لغتي ص4 (5) لغتي ص5 (1)اسرية ص5 (1) نشاط ص 3فصل</v>
+      </c>
+      <c r="E93">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>نوف الزلفي</v>
+      </c>
+      <c r="B94" t="str">
+        <v>رياضيات</v>
+      </c>
+      <c r="C94">
+        <v>24</v>
+      </c>
+      <c r="D94" t="str">
+        <v>(6)رياضيات ص2 (12) رياضيات ص3 (6) بدنية ص3 + معلمة موهبة</v>
+      </c>
+      <c r="E94">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>نور العيدة ( مكرر مكمل من الثانوي)</v>
+      </c>
+      <c r="B95" t="str">
+        <v>رياضيات</v>
+      </c>
+      <c r="C95">
+        <v>6</v>
+      </c>
+      <c r="D95" t="str">
+        <v xml:space="preserve"> ( 6 )  رياضيات ص6 + مسند ( 18) ثانوي + منسقة قدرات وتحصيلي</v>
+      </c>
+      <c r="E95">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>هدى المطيري ( مكرر مكمل من الثانوي)</v>
+      </c>
+      <c r="B96" t="str">
+        <v>كيمياء</v>
+      </c>
+      <c r="C96">
+        <v>2</v>
+      </c>
+      <c r="D96" t="str">
+        <v>(2) بدنية ص5 + مسند ( 23) ثانوي</v>
+      </c>
+      <c r="E96">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>سلطانة العتيبي ( مكرر مكمل من الثانوي)</v>
+      </c>
+      <c r="B97" t="str">
+        <v>فيزياء</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+      <c r="D97" t="str">
+        <v>(1) اسرية ص6 + ( 18 ) ثانوي + ( 5) متوسط</v>
+      </c>
+      <c r="E97">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>نوف العتيبي ( مكرر مكمل من الثانوي )</v>
+      </c>
+      <c r="B98" t="str">
+        <v>لغة عربية</v>
+      </c>
+      <c r="C98">
+        <v>2</v>
+      </c>
+      <c r="D98" t="str">
+        <v>(2) رقمية ص1 + (22) مسند ثانوي</v>
+      </c>
+      <c r="E98">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>بدور  البقمي  ( مكرر مكمل من المتوسط)</v>
+      </c>
+      <c r="B99" t="str">
+        <v>رياضيات</v>
+      </c>
+      <c r="C99">
+        <v>6</v>
+      </c>
+      <c r="D99" t="str">
+        <v>(6)رياضيات ص5 + مسند ( 18)  متوسط</v>
+      </c>
+      <c r="E99">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>منى الخلف</v>
+      </c>
+      <c r="B100" t="str">
+        <v>علوم</v>
+      </c>
+      <c r="C100">
+        <v>20</v>
+      </c>
+      <c r="D100" t="str">
+        <v xml:space="preserve"> (8) علوم ص3 (4) علوم ص4 (4) علوم ص5  (4) علوم ص6 + مسند (4) بالمتوسط</v>
+      </c>
+      <c r="E100">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v xml:space="preserve"> عهود الرويلي </v>
+      </c>
+      <c r="B101" t="str">
+        <v>انجليزي</v>
+      </c>
+      <c r="C101">
+        <v>20</v>
+      </c>
+      <c r="D101" t="str">
+        <v>(3) انجليزي وزاري ص4 ( 2) انجليزي اثرائي ص4  ( 3) انجليزي وزاري ص5 (2) انجليزي اثرائي ص5 (3) انجليزي وزاري ص6 (2)انجليزي اثرائي ص6 (3) بدنية ص2 (2) نشاط ص6 + (4) kg</v>
+      </c>
+      <c r="E101">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v xml:space="preserve">هدى البكري </v>
+      </c>
+      <c r="B102" t="str">
+        <v>فنية</v>
+      </c>
+      <c r="C102">
+        <v>18</v>
+      </c>
+      <c r="D102" t="str">
+        <v>(2)فنية ص1(2) فنية ص2(4) فنية ص3(1) فنية ص4(1)فنية ص5(1) قنية ص6  (2) بدنية ص4 (1)نشاط ص2 (1) اسرية ص1(1) اسرية ص2(2)اسرية ص3+ مسند (6) حصص بالمتوسط + موجهة صحية ابتدائي</v>
+      </c>
+      <c r="E102">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>إجمالي الحصص</v>
+      </c>
+      <c r="B103">
+        <v>245</v>
+      </c>
+      <c r="C103">
+        <v>245</v>
+      </c>
+      <c r="D103" t="str">
+        <v>تم زيادة ( 14) حصة لتفعيل المواد الاثرائية ورفع مستوى التحصيل فأصبح إجمالي الحصص في الأسبوع 35</v>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v/>
+      </c>
+      <c r="B104" t="str">
+        <v>اسنادات متوسط (بنات)</v>
+      </c>
+      <c r="C104" t="str">
+        <v/>
+      </c>
+      <c r="D104" t="str">
+        <v/>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>المعلم</v>
+      </c>
+      <c r="B105" t="str">
+        <v>المادة</v>
+      </c>
+      <c r="C105" t="str">
+        <v xml:space="preserve">عدد حصص المعلم بالمرحلة </v>
+      </c>
+      <c r="D105" t="str">
+        <v>ملاحظات</v>
+      </c>
+      <c r="E105" t="str">
+        <v>إجمالي نصاب المعلم بعد الاكمال</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v/>
+      </c>
+      <c r="B106" t="str">
+        <v/>
+      </c>
+      <c r="C106" t="str">
+        <v/>
+      </c>
+      <c r="D106" t="str">
+        <v/>
+      </c>
+      <c r="E106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>هدى البكري ( مكرر مكمل من ابتدائي)</v>
+      </c>
+      <c r="B107" t="str">
+        <v>فنية</v>
+      </c>
+      <c r="C107">
+        <v>6</v>
+      </c>
+      <c r="D107" t="str">
+        <v>(2) فنية ص1 (2) فنية ص2 (2) فنية ص + مسند (18) حصة بالابتدائي + موجهة صحية ابتدائي</v>
+      </c>
+      <c r="E107">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v xml:space="preserve">حنان الغربي </v>
+      </c>
+      <c r="B108" t="str">
+        <v>اجتماعيات</v>
+      </c>
+      <c r="C108">
+        <v>11</v>
+      </c>
+      <c r="D108" t="str">
+        <v>(3) اجتماعيات ص1 (3) اجتماعيات ص2(2) اجتماعيات ص3 (2) بدنية 3م (1) اسرية 3م + مسند (13) حصص بالثانوي + مسؤولة المقصف</v>
+      </c>
+      <c r="E108">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>نوير الشمري    ( مكرر مكمل من الثانوي)</v>
+      </c>
+      <c r="B109" t="str">
+        <v>حاسب</v>
+      </c>
+      <c r="C109">
+        <v>6</v>
+      </c>
+      <c r="D109" t="str">
+        <v>(2) رقمية ص1 (2) رقمية ص3 (2) رقمية ص3 + مسند (١0) حصص بالثانوي + (8) حصص بالابتدائي</v>
+      </c>
+      <c r="E109">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>منى الخلف ( مكرر مكمل من الابتدائي )</v>
+      </c>
+      <c r="B110" t="str">
+        <v>علوم</v>
+      </c>
+      <c r="C110">
+        <v>4</v>
+      </c>
+      <c r="D110" t="str">
+        <v>(4) علوم ص1 + مسند (20 ) ابتدائي</v>
+      </c>
+      <c r="E110">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>بدور  البقمي</v>
+      </c>
+      <c r="B111" t="str">
+        <v>رياضيات</v>
+      </c>
+      <c r="C111">
+        <v>18</v>
+      </c>
+      <c r="D111" t="str">
+        <v>(6) رياضيات ص1 (6) رياضيات ص2 (6) رياضيات ص3 + مسند لها (6) ابتدائي</v>
+      </c>
+      <c r="E111">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>ريم الحربي ( مكرر مكمل من الثانوي)</v>
+      </c>
+      <c r="B112" t="str">
+        <v>دين</v>
+      </c>
+      <c r="C112">
+        <v>5</v>
+      </c>
+      <c r="D112" t="str">
+        <v>( 5 ) إسلامية ص3 + مسند ثانوي 19 ثانوي</v>
+      </c>
+      <c r="E112">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>اماني فهمي ( مكرر مكمل من الثانوي)</v>
+      </c>
+      <c r="B113" t="str">
+        <v>احياء</v>
+      </c>
+      <c r="C113">
+        <v>4</v>
+      </c>
+      <c r="D113" t="str">
+        <v>(4) علوم ص2 + مسند لها (20) ثانوي</v>
+      </c>
+      <c r="E113">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>سلطانة العتيبي ( مكرر مكمل من الثانوي)</v>
+      </c>
+      <c r="B114" t="str">
+        <v>فيزياء</v>
+      </c>
+      <c r="C114">
+        <v>5</v>
+      </c>
+      <c r="D114" t="str">
+        <v>(4) علوم ص3 (1) نشاط ص3 + مسند لها (18 ) ثانوي + ( 1) ابتدائي + منسقة نافس</v>
+      </c>
+      <c r="E114">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>امل العنزي ( مكرر مكمل من الثانوي)</v>
+      </c>
+      <c r="B115" t="str">
+        <v>انجليزي</v>
+      </c>
+      <c r="C115">
+        <v>5</v>
+      </c>
+      <c r="D115" t="str">
+        <v>(4) انجليزي ص3 (1) أسرية ص3 + مسند (19) حصة بالثانوي + منسقة اختبارات steep</v>
+      </c>
+      <c r="E115">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>حنان العنزي</v>
+      </c>
+      <c r="B116" t="str">
+        <v>انجليزي</v>
+      </c>
+      <c r="C116">
+        <v>11</v>
+      </c>
+      <c r="D116" t="str">
+        <v>(4) انجليزي ص1(4) انجليزي ص2(1)اسرية ص2 (2) بدنية ص2+ مسند لها (11) حصة ثانوي+(3) ابتدائي</v>
+      </c>
+      <c r="E116">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>الجوهرة المخلفي</v>
+      </c>
+      <c r="B117" t="str">
+        <v>لغة عربية</v>
+      </c>
+      <c r="C117">
+        <v>17</v>
+      </c>
+      <c r="D117" t="str">
+        <v>(5) لغتي ص1 (5) لغتي ص2(4) لغتي ص3 (2) بدنية ص1 (1) نشاط ص1 + مسند (7) حصص بالابتدائي + منسقة اختبارات مركزية</v>
+      </c>
+      <c r="E117">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>نهال الشبرمي</v>
+      </c>
+      <c r="B118" t="str">
+        <v>إسلامية</v>
+      </c>
+      <c r="C118">
+        <v>13</v>
+      </c>
+      <c r="D118" t="str">
+        <v>(5) إسلامية ص1 (5) إسلامية ص2  (٢)  تفكير ناقد ص3  (1) نشاط ص2 + مسند (7) حصص بالابتدائي + (4) kg + منسقة الصيانة والمشتريات</v>
+      </c>
+      <c r="E118">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>إجمالي الحصص</v>
+      </c>
+      <c r="B119">
+        <v>105</v>
+      </c>
+      <c r="C119">
+        <v>105</v>
+      </c>
+      <c r="D119" t="str">
+        <v/>
+      </c>
+      <c r="E119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v/>
+      </c>
+      <c r="B120" t="str">
+        <v>اسنادات ثانوي (بنات)</v>
+      </c>
+      <c r="C120" t="str">
+        <v/>
+      </c>
+      <c r="D120" t="str">
+        <v/>
+      </c>
+      <c r="E120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>المعلم</v>
+      </c>
+      <c r="B121" t="str">
+        <v>المادة</v>
+      </c>
+      <c r="C121" t="str">
+        <v>عدد حصص المعلم بالمدرسة</v>
+      </c>
+      <c r="D121" t="str">
+        <v>الإسناد</v>
+      </c>
+      <c r="E121" t="str">
+        <v>إجمالي نصاب المعلم</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>حنان الغربي ( مكرر مكمل  متوسط )</v>
+      </c>
+      <c r="B122" t="str">
+        <v>اجتماعيات</v>
+      </c>
+      <c r="C122">
+        <v>13</v>
+      </c>
+      <c r="D122" t="str">
+        <v>(6) تاريخ ص2 (6) بدنية ص3 (1) نشاط ص3 فصل + مسند (11) حصص بالمتوسط + مسؤولة المقصف</v>
+      </c>
+      <c r="E122">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v xml:space="preserve">نوف العتيبي </v>
+      </c>
+      <c r="B123" t="str">
+        <v>لغة عربية</v>
+      </c>
+      <c r="C123">
+        <v>22</v>
+      </c>
+      <c r="D123" t="str">
+        <v>(8) كفايات ص1(8) كفايات ص2 (4) بحث ومعلومات ص3 (2) نشاط ص2  + مسند (2) ابتدائي + أمينة مصادر</v>
+      </c>
+      <c r="E123">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>ريم الحربي</v>
+      </c>
+      <c r="B124" t="str">
+        <v>إسلامية</v>
+      </c>
+      <c r="C124">
+        <v>19</v>
+      </c>
+      <c r="D124" t="str">
+        <v>(6) تفكير ناقد ص1 (8) قرآن وتفسيره صف1 (5) مجال اختياري مهارات إدارية + مسند (5) متوسط</v>
+      </c>
+      <c r="E124">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>سلطانة البقمي</v>
+      </c>
+      <c r="B125" t="str">
+        <v>رياضيات</v>
+      </c>
+      <c r="C125">
+        <v>25</v>
+      </c>
+      <c r="D125" t="str">
+        <v xml:space="preserve">(8) رياضيات ص3 (10) رياضيات ص1 ( 4) بدنية ص1 (3) نشاط ص3 </v>
+      </c>
+      <c r="E125">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>نور العيدة</v>
+      </c>
+      <c r="B126" t="str">
+        <v>رياضيات</v>
+      </c>
+      <c r="C126">
+        <v>18</v>
+      </c>
+      <c r="D126" t="str">
+        <v>(10) رياضيات ص2 (3) نشاط ص2 (5) مجال اختياري تنمية مستدامة ص3 + مسند (6) ابتدائي+ منسقة قدرات وتحصيلي</v>
+      </c>
+      <c r="E126">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>سلطانة العتيبي</v>
+      </c>
+      <c r="B127" t="str">
+        <v>فيزياء</v>
+      </c>
+      <c r="C127">
+        <v>18</v>
+      </c>
+      <c r="D127" t="str">
+        <v>(8) فيزياء ص2 (10) فيزياء ص3 + مسند (5) متوسط + (1) ابتدائي  + منسقة نافس</v>
+      </c>
+      <c r="E127">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>هدى المطيري</v>
+      </c>
+      <c r="B128" t="str">
+        <v>كيمياء</v>
+      </c>
+      <c r="C128">
+        <v>23</v>
+      </c>
+      <c r="D128" t="str">
+        <v>(6) كيمياء ص1 (10) كيمياء ص2 (6) كيمياء ص3 (1) نشاط ص1 فصل + (2) مسند ابتدائي</v>
+      </c>
+      <c r="E128">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>أماني فهمي</v>
+      </c>
+      <c r="B129" t="str">
+        <v>أحياء</v>
+      </c>
+      <c r="C129">
+        <v>20</v>
+      </c>
+      <c r="D129" t="str">
+        <v>(6) أحياء ص1 (8) أحياء ص2 (9) علم الأرض ص3 + مسند (4) متوسط</v>
+      </c>
+      <c r="E129">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>حنان العنزي (مكرر مكمل من متوسط )</v>
+      </c>
+      <c r="B130" t="str">
+        <v>انجليزي</v>
+      </c>
+      <c r="C130">
+        <v>11</v>
+      </c>
+      <c r="D130" t="str">
+        <v>(10) انجليزي ص1 (1) نشاط ص1 فصل + مسند (11) متوسط +( 3) ابتدائي</v>
+      </c>
+      <c r="E130">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v xml:space="preserve">أمل العنزي </v>
+      </c>
+      <c r="B131" t="str">
+        <v>انجليزي</v>
+      </c>
+      <c r="C131">
+        <v>19</v>
+      </c>
+      <c r="D131" t="str">
+        <v>(8) انجليزي ص3 (10) انجليزي ص2 (1) نشاط ص2 فصل + مسند (5) متوسط + منسقة اختبارات steep</v>
+      </c>
+      <c r="E131">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v xml:space="preserve">نوير الشمري </v>
+      </c>
+      <c r="B132" t="str">
+        <v>حاسب</v>
+      </c>
+      <c r="C132">
+        <v>10</v>
+      </c>
+      <c r="D132" t="str">
+        <v>(٦) تقنية رقمية ص1 (4) رقمية ص3  + مسند (٦) حصص بالمتوسط + (8) حصص بالابتدائي</v>
+      </c>
+      <c r="E132">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>إجمالي الحصص</v>
+      </c>
+      <c r="B133">
+        <v>198</v>
+      </c>
+      <c r="C133">
+        <v>198</v>
+      </c>
+      <c r="D133" t="str">
+        <v>تم زيادة ( 6) حصص لتفعيل البرامج الاثرائية ورفع مستوى التحصيل فأصبحت إجمالي الحصص 198</v>
+      </c>
+      <c r="E133" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A44:E44"/>
-  </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E75"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E133"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -18797,6 +19779,2291 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E133"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v/>
+      </c>
+      <c r="B1" t="str">
+        <v>اسنادات قطاع البنين</v>
+      </c>
+      <c r="C1" t="str">
+        <v/>
+      </c>
+      <c r="D1" t="str">
+        <v/>
+      </c>
+      <c r="E1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v/>
+      </c>
+      <c r="B4" t="str">
+        <v>اسنادات ابتدائي (بنين)</v>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>المعلم</v>
+      </c>
+      <c r="B6" t="str">
+        <v>المادة</v>
+      </c>
+      <c r="C6" t="str">
+        <v>عدد حصص المعلم بالمدرسة</v>
+      </c>
+      <c r="D6" t="str">
+        <v>الإسناد</v>
+      </c>
+      <c r="E6" t="str">
+        <v>إجمالي نصاب المعلم</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>العفيفي عبد الجواد</v>
+      </c>
+      <c r="B7" t="str">
+        <v>معلم صف أول</v>
+      </c>
+      <c r="C7" t="str">
+        <v>24</v>
+      </c>
+      <c r="D7" t="str">
+        <v>(٨) لغتي ص١+ (٤) اسلاميات ص١+ (٥) رياضيات ص١+ (٢) بدنية ص١+ (١) مهارات حياتية ص١ + (1) فنية ص١ + (3) علوم ص1</v>
+      </c>
+      <c r="E7" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>محمود عبدالحسيب</v>
+      </c>
+      <c r="B8" t="str">
+        <v>معلم صف أول</v>
+      </c>
+      <c r="C8" t="str">
+        <v>24</v>
+      </c>
+      <c r="D8" t="str">
+        <v>(٨) لغتي ص١+ (٤) اسلاميات ص١+ (٥) رياضيات ص١+ (٢) بدنية ص١+ (١) مهارات حياتية ص١ + (1) فنية ص١ + (3) علوم ص1</v>
+      </c>
+      <c r="E8" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>عبد العزيز يونس</v>
+      </c>
+      <c r="B9" t="str">
+        <v>معلم صف ثاني</v>
+      </c>
+      <c r="C9" t="str">
+        <v>24</v>
+      </c>
+      <c r="D9" t="str">
+        <v xml:space="preserve">(١٤) لغتي ص٢ فصلين + (١٠) اسلاميات ص٢ فصلين </v>
+      </c>
+      <c r="E9" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>حسن عزالدين مبروك</v>
+      </c>
+      <c r="B10" t="str">
+        <v>معلم صف ثالث</v>
+      </c>
+      <c r="C10" t="str">
+        <v>24</v>
+      </c>
+      <c r="D10" t="str">
+        <v>(١٤) لغتي ص٣ فصلين(2/4 ، 3/4) + (١٠) اسلاميات ص٣ فصلين +(٢) مهارات حياتية ص٣ فصلين</v>
+      </c>
+      <c r="E10" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>سلمان حمد الفراج</v>
+      </c>
+      <c r="B11" t="str">
+        <v>اسلاميات</v>
+      </c>
+      <c r="C11" t="str">
+        <v>24</v>
+      </c>
+      <c r="D11" t="str">
+        <v>(١٢) اسلاميات ص٤ فصلين (2/4 ،3/4)+ (٨) اسلاميات ص٥+ (٤) اسلاميات ص٦ فصلين</v>
+      </c>
+      <c r="E11" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>محمد الغباشي</v>
+      </c>
+      <c r="B12" t="str">
+        <v>لغة عربية</v>
+      </c>
+      <c r="C12" t="str">
+        <v>25</v>
+      </c>
+      <c r="D12" t="str">
+        <v>(٥) لغتي ص 4 فصل(2/4) + (١٠) لغتي ص٥ فصلين +(١٠) لغتي ص٦ فصلين</v>
+      </c>
+      <c r="E12" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>طارق عبدالظاهر</v>
+      </c>
+      <c r="B13" t="str">
+        <v>رياضيات</v>
+      </c>
+      <c r="C13" t="str">
+        <v>24</v>
+      </c>
+      <c r="D13" t="str">
+        <v>(18) رياضيات ص٤ +(6) رياضيات ص٥ فصل</v>
+      </c>
+      <c r="E13" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v xml:space="preserve">احمد سالم </v>
+      </c>
+      <c r="B14" t="str">
+        <v>رياضيات</v>
+      </c>
+      <c r="C14" t="str">
+        <v>24</v>
+      </c>
+      <c r="D14" t="str">
+        <v>(١٢) رياضيات ص٦ فصلين  + مسند (6) رياضيات ص5 فصل + (5) نشاط ص4 وص5 + (1) نشاط ص6 فصل</v>
+      </c>
+      <c r="E14" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v xml:space="preserve">عمرو محمد </v>
+      </c>
+      <c r="B15" t="str">
+        <v>رياضيات</v>
+      </c>
+      <c r="C15" t="str">
+        <v>24</v>
+      </c>
+      <c r="D15" t="str">
+        <v xml:space="preserve">(12) رياضيات ص٢ ب فصلين+(12) رياضيات ص٣ فصلين </v>
+      </c>
+      <c r="E15" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>ربيع عوض</v>
+      </c>
+      <c r="B16" t="str">
+        <v>لغة انجليزية</v>
+      </c>
+      <c r="C16" t="str">
+        <v>24</v>
+      </c>
+      <c r="D16" t="str">
+        <v>(٦) E ص٥ + (٦) E ص٦ + (٩) E ص٤ + (2) انجليزي إثرائي ص6 + (1) نشاط ص6 فصل</v>
+      </c>
+      <c r="E16" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>محمد السيد</v>
+      </c>
+      <c r="B17" t="str">
+        <v>لغة انجليزية</v>
+      </c>
+      <c r="C17" t="str">
+        <v>24</v>
+      </c>
+      <c r="D17" t="str">
+        <v xml:space="preserve"> (٦) E ص٣ + + (٤) E اثرائي ص3  + (٦) E اثرائي ص٤ + (2) E اثرائي ص٦+ (٤) E اثراىي ص٥ +(2) انجليزي اثرائي ص2 فصل</v>
+      </c>
+      <c r="E17" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>احمد حسنين</v>
+      </c>
+      <c r="B18" t="str">
+        <v>لغة انجليزية</v>
+      </c>
+      <c r="C18" t="str">
+        <v>24</v>
+      </c>
+      <c r="D18" t="str">
+        <v>(6) E ص١+ (٤) E اثرائي ص١+ (٦) E ص٢ + (2) E اثرائي ص٢ فصل+ (4) ماث ص١ + (٢) ساينس ص١</v>
+      </c>
+      <c r="E18" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v xml:space="preserve"> ايمن محمد </v>
+      </c>
+      <c r="B19" t="str">
+        <v>علوم</v>
+      </c>
+      <c r="C19" t="str">
+        <v>24</v>
+      </c>
+      <c r="D19" t="str">
+        <v>(٦) علوم ص2 فصلين+ (8) علوم ص٣ فصلين+ (٨) علوم ص4 فصلين(1/4،2/4)+ (٢) بدنية ص5 فصل (2/5)</v>
+      </c>
+      <c r="E19" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>مصطفى عبدالتواب</v>
+      </c>
+      <c r="B20" t="str">
+        <v>علوم</v>
+      </c>
+      <c r="C20" t="str">
+        <v>24</v>
+      </c>
+      <c r="D20" t="str">
+        <v>(٨) علوم ص٥  + (٨) علوم ص٦ + (٤) علوم ص٤ + (٤) اجتماعيات ص٦</v>
+      </c>
+      <c r="E20" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>محمد إبراهيم</v>
+      </c>
+      <c r="B21" t="str">
+        <v>لغة عربية</v>
+      </c>
+      <c r="C21" t="str">
+        <v>24</v>
+      </c>
+      <c r="D21" t="str">
+        <v>(١٠) لغتي ص٤ فصلين(1/4،3/4) + (٤) اسلاميات ص4 فصل(1/4) + (١٠) اجتماعيات ص٤ فصلين ص٥ فصلين</v>
+      </c>
+      <c r="E21" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>رامي يسن معروف</v>
+      </c>
+      <c r="B22" t="str">
+        <v>فنية</v>
+      </c>
+      <c r="C22" t="str">
+        <v>24</v>
+      </c>
+      <c r="D22" t="str">
+        <v>(٤) فنية ص٢+ (٤) فنية ص٣ + (٣) فنية ص٤ + (٢) فنية ص٥ + (٢) فنية ص٦ + (٩) مهارات حياتية ص٢، ص٤، ص٥، ص٦</v>
+      </c>
+      <c r="E22" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>محمود وحش</v>
+      </c>
+      <c r="B23" t="str">
+        <v>بدنية</v>
+      </c>
+      <c r="C23" t="str">
+        <v>24</v>
+      </c>
+      <c r="D23" t="str">
+        <v>(6) بدنية ص٣ + (٦) بدنية ص٤ + (6) بدنية ص٢  + (2) بدنية ص٥ +  (4) بدنية ص6</v>
+      </c>
+      <c r="E23" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>آمير جلال</v>
+      </c>
+      <c r="B24" t="str">
+        <v>رقمية</v>
+      </c>
+      <c r="C24" t="str">
+        <v>24</v>
+      </c>
+      <c r="D24" t="str">
+        <v xml:space="preserve">(2) رقمية ص١+ (٤) رقمية ص٢+ (٤) رقمية ص٣ + (٦) رقمية ص٤ + (٤) رقمية ص٥ + (٤) رقمية ص٦ </v>
+      </c>
+      <c r="E24" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="A25" t="str">
+        <v>إجمالي الحصص</v>
+      </c>
+      <c r="B25" t="str">
+        <v>396</v>
+      </c>
+      <c r="C25" t="str">
+        <v>433</v>
+      </c>
+      <c r="D25" t="str" xml:space="preserve">
+        <v xml:space="preserve">اضافة عدد (٣٨) حصة اثرائي لغة انجليزية + (١٢) اثرائي رقمية صفوف أولية فيصبح مجموع الحصص الاثرائية (٥٠) حصة _x000d_
+تخفيض (١) حصة فنية الصف الاول باجمالي (٢) حصة_x000d_
+تخفيض (١) حصة بدنية الصف الاول باجمالي (٢) حصة_x000d_
+تخفيض (١) حصة اسلاميات الصف الاول باجمالي (٢) حصة_x000d_
+تخفيض (١) حصة اسلاميات صفوف عليا باجمالي (٧) حصص_x000d_
+تخفيض حصة رقمية صف 1_x000d_
+استبدال  (٣٢) حصة نشاط  مع الحصص الاثرائية _x000d_
+(٥٠) - (٣٢) = (١٨) حصة </v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v/>
+      </c>
+      <c r="B26" t="str">
+        <v/>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v/>
+      </c>
+      <c r="B27" t="str">
+        <v>اسنادات متوسط (بنين)</v>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v/>
+      </c>
+      <c r="B28" t="str">
+        <v/>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>المعلم</v>
+      </c>
+      <c r="B29" t="str">
+        <v>المادة</v>
+      </c>
+      <c r="C29" t="str">
+        <v>عدد حصص المعلم بالمدرسة</v>
+      </c>
+      <c r="D29" t="str">
+        <v>الإسناد</v>
+      </c>
+      <c r="E29" t="str">
+        <v>إجمالي نصاب المعلم</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>فواز المطيري</v>
+      </c>
+      <c r="B30" t="str">
+        <v>اسلاميات</v>
+      </c>
+      <c r="C30" t="str">
+        <v>25</v>
+      </c>
+      <c r="D30" t="str">
+        <v xml:space="preserve"> (5) اسلاميات ص1 فصل 1/1 +(10) اسلاميات ص2 فصلين 2/1 - 2/2 + (10) اسلاميات ص 3 فصل 3/1 - 3/2 </v>
+      </c>
+      <c r="E30" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>احمد صوفي</v>
+      </c>
+      <c r="B31" t="str">
+        <v>لغة عربية</v>
+      </c>
+      <c r="C31" t="str">
+        <v>26</v>
+      </c>
+      <c r="D31" t="str">
+        <v xml:space="preserve"> (15) لغتي ص1 متوسط   +  (٥) اسلاميات ص2  فصل 2/3  +(6) تفكير ناقد متوسط ص٣</v>
+      </c>
+      <c r="E31" t="str">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>محمد سمير</v>
+      </c>
+      <c r="B32" t="str">
+        <v>لغة عربية</v>
+      </c>
+      <c r="C32" t="str">
+        <v>27</v>
+      </c>
+      <c r="D32" t="str">
+        <v xml:space="preserve">(15) لغتي ص2 م + (12 ) لغتي ص 3 </v>
+      </c>
+      <c r="E32" t="str">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>ماهر الحربي</v>
+      </c>
+      <c r="B33" t="str">
+        <v>رياضيات</v>
+      </c>
+      <c r="C33" t="str">
+        <v>24</v>
+      </c>
+      <c r="D33" t="str">
+        <v>(18) رياضيات ص١+ (6) رياضيات ص2م فصل 2/3</v>
+      </c>
+      <c r="E33" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>حسن السيد</v>
+      </c>
+      <c r="B34" t="str">
+        <v>رياضيات</v>
+      </c>
+      <c r="C34" t="str">
+        <v>30</v>
+      </c>
+      <c r="D34" t="str">
+        <v>(18) رياضيات ص3م  + (6) رياضيات ص2م فصل 2/2 - 2/3</v>
+      </c>
+      <c r="E34" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v xml:space="preserve">سلمان الصادق </v>
+      </c>
+      <c r="B35" t="str">
+        <v>لغة انجليزية</v>
+      </c>
+      <c r="C35" t="str">
+        <v>24</v>
+      </c>
+      <c r="D35" t="str">
+        <v xml:space="preserve">(12) انجليزي ص٢متوسط +(12) انجليزي ص٣ متوسط  </v>
+      </c>
+      <c r="E35" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>مصطفى فتحي</v>
+      </c>
+      <c r="B36" t="str">
+        <v>لغة انجليزية</v>
+      </c>
+      <c r="C36" t="str">
+        <v>12</v>
+      </c>
+      <c r="D36" t="str">
+        <v xml:space="preserve"> (١٢) انجليزي ص١ متوسط + مكمل (١٢) حصة بالثانوي </v>
+      </c>
+      <c r="E36" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>فارس الجندي</v>
+      </c>
+      <c r="B37" t="str">
+        <v>علوم</v>
+      </c>
+      <c r="C37" t="str">
+        <v>24</v>
+      </c>
+      <c r="D37" t="str">
+        <v xml:space="preserve">(12) علوم ص١ +(12) علوم ص٢ </v>
+      </c>
+      <c r="E37" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v xml:space="preserve">محمد العشماوي </v>
+      </c>
+      <c r="B38" t="str">
+        <v>علوم</v>
+      </c>
+      <c r="C38" t="str">
+        <v>27</v>
+      </c>
+      <c r="D38" t="str">
+        <v>(12) علوم ص٣ +(10) اسلاميات ص1 فصل 1/2 - 1/3 + ( 5 ) اسلاميات  صف 3 فصل 3/3</v>
+      </c>
+      <c r="E38" t="str">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>عبدالعزيز الربيعان</v>
+      </c>
+      <c r="B39" t="str">
+        <v>اجتماعيات</v>
+      </c>
+      <c r="C39" t="str">
+        <v>24</v>
+      </c>
+      <c r="D39" t="str">
+        <v xml:space="preserve">(24) اجتماعيات (9) ص١ + (9 ) ص٢ +( 6 ) ص٣ متوسط   </v>
+      </c>
+      <c r="E39" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>محمود صابر</v>
+      </c>
+      <c r="B40" t="str">
+        <v>فنية</v>
+      </c>
+      <c r="C40" t="str">
+        <v>27</v>
+      </c>
+      <c r="D40" t="str">
+        <v xml:space="preserve">(18) فنية ص١ ص٢ ص٣ + (9) حياتية ص١ + ص2 + ص3 فصل </v>
+      </c>
+      <c r="E40" t="str">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>حسين عويضة (مكمل مكرر من الثانوي)</v>
+      </c>
+      <c r="B41" t="str">
+        <v>بدنية</v>
+      </c>
+      <c r="C41" t="str">
+        <v>12</v>
+      </c>
+      <c r="D41" t="str">
+        <v>( 6) بدنية ص2 متوسط +  (6) بدنية ص٣ متوسط + مكمل (١٣) حصة بالثانوي</v>
+      </c>
+      <c r="E41" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>محمد عبد الله (مكمل مكرر من الثانوي)</v>
+      </c>
+      <c r="B42" t="str">
+        <v>رقمية</v>
+      </c>
+      <c r="C42" t="str">
+        <v>8</v>
+      </c>
+      <c r="D42" t="str">
+        <v>(6) رقمية  ص٣ متوسط+ (2) رقمية  ص٢ متوسط فصل 3 + مكمل (١٨) حصة بالثانوي</v>
+      </c>
+      <c r="E42" t="str">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v xml:space="preserve">محمود جمعه </v>
+      </c>
+      <c r="B43" t="str">
+        <v>رقمية</v>
+      </c>
+      <c r="C43" t="str">
+        <v>25</v>
+      </c>
+      <c r="D43" t="str">
+        <v>(٦) رقمية  ص١متوسط +(4) رقمية  ص٢ متوسط فصل 1  + فصل 2  + ( 6) بدنية ص1 متوسط + (3) نشاط ص1 + (3) نشاط ص 3 + (3) نشاط ص2</v>
+      </c>
+      <c r="E43" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v/>
+      </c>
+      <c r="B44" t="str">
+        <v/>
+      </c>
+      <c r="C44" t="str">
+        <v>315</v>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v/>
+      </c>
+      <c r="B45" t="str">
+        <v/>
+      </c>
+      <c r="C45" t="str">
+        <v/>
+      </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v/>
+      </c>
+      <c r="B46" t="str">
+        <v>اسنادات ثانوي (بنين)</v>
+      </c>
+      <c r="C46" t="str">
+        <v/>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v/>
+      </c>
+      <c r="B47" t="str">
+        <v/>
+      </c>
+      <c r="C47" t="str">
+        <v/>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>المعلم</v>
+      </c>
+      <c r="B48" t="str">
+        <v>المادة</v>
+      </c>
+      <c r="C48" t="str">
+        <v>عدد حصص المعلم بالمدرسة</v>
+      </c>
+      <c r="D48" t="str">
+        <v>الإسناد</v>
+      </c>
+      <c r="E48" t="str">
+        <v>عدد حصص المعلم بالمدرسة</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>احمد نصر</v>
+      </c>
+      <c r="B49" t="str">
+        <v xml:space="preserve">لغة عربية </v>
+      </c>
+      <c r="C49" t="str">
+        <v>24</v>
+      </c>
+      <c r="D49" t="str">
+        <v>20 كفايات 1ث من 6:2 +4 كفايات 2ث 7</v>
+      </c>
+      <c r="E49" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v xml:space="preserve">هشام رسمي </v>
+      </c>
+      <c r="B50" t="str">
+        <v xml:space="preserve">لغة عربية </v>
+      </c>
+      <c r="C50" t="str">
+        <v>27</v>
+      </c>
+      <c r="D50" t="str">
+        <v xml:space="preserve">24 حصة كفايات  2ث 6فصول من 6:1+ 3 حصص 2-ث نون </v>
+      </c>
+      <c r="E50" t="str">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v xml:space="preserve">حسن الخطيب </v>
+      </c>
+      <c r="B51" t="str">
+        <v xml:space="preserve">لغة عربية </v>
+      </c>
+      <c r="C51" t="str">
+        <v>24</v>
+      </c>
+      <c r="D51" t="str">
+        <v>14 مهارا ت بحث 3 ث كامل + 6 كفايات 1ث نون  +4 كفايات 1ث 1</v>
+      </c>
+      <c r="E51" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v xml:space="preserve">عبد العزيز الربيعان </v>
+      </c>
+      <c r="B52" t="str">
+        <v xml:space="preserve">لغة عربية </v>
+      </c>
+      <c r="C52" t="str">
+        <v>26</v>
+      </c>
+      <c r="D52" t="str">
+        <v>21 تاريخ 2ث كامل+2 تاريخ 2ث نون +3 تفسير 1ث2 نون</v>
+      </c>
+      <c r="E52" t="str">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>خالد المطيري</v>
+      </c>
+      <c r="B53" t="str">
+        <v xml:space="preserve">اسلاميات </v>
+      </c>
+      <c r="C53" t="str">
+        <v>27</v>
+      </c>
+      <c r="D53" t="str">
+        <v xml:space="preserve">24 تفسير وقران 1ث كامل + 3 تفسير 1ث1 نون </v>
+      </c>
+      <c r="E53" t="str">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v xml:space="preserve">حسام السيد </v>
+      </c>
+      <c r="B54" t="str">
+        <v xml:space="preserve">رياضيات </v>
+      </c>
+      <c r="C54" t="str">
+        <v>28</v>
+      </c>
+      <c r="D54" t="str">
+        <v xml:space="preserve">20 صف2ث 4 فصول 4:1+4 نون صف2ث + 4 صف3ث1 </v>
+      </c>
+      <c r="E54" t="str">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v xml:space="preserve">محمد سليم </v>
+      </c>
+      <c r="B55" t="str">
+        <v xml:space="preserve">رياضيات </v>
+      </c>
+      <c r="C55" t="str">
+        <v>28</v>
+      </c>
+      <c r="D55" t="str">
+        <v>20صف 3ث من 6:2 +8 حصص 1 ث نون 1-2</v>
+      </c>
+      <c r="E55" t="str">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v xml:space="preserve">وليد الصدة </v>
+      </c>
+      <c r="B56" t="str">
+        <v xml:space="preserve">رياضيات </v>
+      </c>
+      <c r="C56" t="str">
+        <v>24</v>
+      </c>
+      <c r="D56" t="str">
+        <v xml:space="preserve">20 1ث  4 فصول من4:1+ 4 حصص 3ث7 </v>
+      </c>
+      <c r="E56" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>وسيم عبد ربه</v>
+      </c>
+      <c r="B57" t="str">
+        <v xml:space="preserve">رياضيات </v>
+      </c>
+      <c r="C57" t="str">
+        <v>25</v>
+      </c>
+      <c r="D57" t="str">
+        <v>10 صف 1ث  6:5+ 15 صف 2ث من 7:5</v>
+      </c>
+      <c r="E57" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v xml:space="preserve">أحمد طاهر بهيدي </v>
+      </c>
+      <c r="B58" t="str">
+        <v xml:space="preserve">كيمياء </v>
+      </c>
+      <c r="C58" t="str">
+        <v>27</v>
+      </c>
+      <c r="D58" t="str">
+        <v>18 صف 1ث كامل + 6 حصص 1 ث نون 2:1 + 3 علم أرض 3ث7</v>
+      </c>
+      <c r="E58" t="str">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v xml:space="preserve">أحمد محمد مصباح </v>
+      </c>
+      <c r="B59" t="str">
+        <v xml:space="preserve">كيمياء </v>
+      </c>
+      <c r="C59" t="str">
+        <v>25</v>
+      </c>
+      <c r="D59" t="str">
+        <v>25 حصة صف2 ث من 5:1</v>
+      </c>
+      <c r="E59" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>محمد متولي</v>
+      </c>
+      <c r="B60" t="str">
+        <v xml:space="preserve">كيمياء </v>
+      </c>
+      <c r="C60" t="str">
+        <v>26</v>
+      </c>
+      <c r="D60" t="str">
+        <v>21 صف 3 ث كامل + 5 حصص 2 ث نون</v>
+      </c>
+      <c r="E60" t="str">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>حسن جوده</v>
+      </c>
+      <c r="B61" t="str">
+        <v>كيمياء - فيزياء</v>
+      </c>
+      <c r="C61" t="str">
+        <v>25</v>
+      </c>
+      <c r="D61" t="str">
+        <v>10كيمياء  صف 2ث 7:6+15فيزياء  صف 3ث 3:1</v>
+      </c>
+      <c r="E61" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>فريج السعيد</v>
+      </c>
+      <c r="B62" t="str">
+        <v xml:space="preserve">فيزياء </v>
+      </c>
+      <c r="C62" t="str">
+        <v>24</v>
+      </c>
+      <c r="D62" t="str">
+        <v xml:space="preserve"> 20صف 3ث 7:4 + 4 حصص 2 ث7</v>
+      </c>
+      <c r="E62" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v xml:space="preserve">سلمان محمد </v>
+      </c>
+      <c r="B63" t="str">
+        <v xml:space="preserve">فيزياء </v>
+      </c>
+      <c r="C63" t="str">
+        <v>28</v>
+      </c>
+      <c r="D63" t="str">
+        <v xml:space="preserve">24 حصة صف2 ث 6 فصول 6:1 + 4 حصص 2ث نون </v>
+      </c>
+      <c r="E63" t="str">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v xml:space="preserve">محمد عبد المنعم </v>
+      </c>
+      <c r="B64" t="str">
+        <v xml:space="preserve">أحياء </v>
+      </c>
+      <c r="C64" t="str">
+        <v>27</v>
+      </c>
+      <c r="D64" t="str">
+        <v>18 صف 1ث كامل + 3 علم ارض ص ثالث6 +6 حصص 1 ث نون 1و2</v>
+      </c>
+      <c r="E64" t="str">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>حسن ابوغنيمة</v>
+      </c>
+      <c r="B65" t="str">
+        <v xml:space="preserve">أحياء </v>
+      </c>
+      <c r="C65" t="str">
+        <v>20</v>
+      </c>
+      <c r="D65" t="str">
+        <v>20 حصة 2ث 4:1+4أحياء  2ث نون+ مسند له كلاسيرا</v>
+      </c>
+      <c r="E65" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>محمد علي</v>
+      </c>
+      <c r="B66" t="str">
+        <v xml:space="preserve">أحياء </v>
+      </c>
+      <c r="C66" t="str">
+        <v>27</v>
+      </c>
+      <c r="D66" t="str">
+        <v>15 علم أرض 3ث من 5:3 + 12 أحياءص2ث 7:5</v>
+      </c>
+      <c r="E66" t="str">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v xml:space="preserve">مصطفى محمد </v>
+      </c>
+      <c r="B67" t="str">
+        <v xml:space="preserve">لغة انجليزية </v>
+      </c>
+      <c r="C67" t="str">
+        <v>26</v>
+      </c>
+      <c r="D67" t="str">
+        <v>24حصة اث كامل + 2 حصة 1ث نون 1</v>
+      </c>
+      <c r="E67" t="str">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v xml:space="preserve">عبد الرحمن شطا </v>
+      </c>
+      <c r="B68" t="str">
+        <v xml:space="preserve">لغة انجليزية </v>
+      </c>
+      <c r="C68" t="str">
+        <v>25</v>
+      </c>
+      <c r="D68" t="str">
+        <v>20حصة 2 ث من5:1+ 4 حصص 3ث1+ 1 حصة نون 2ث</v>
+      </c>
+      <c r="E68" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v xml:space="preserve">مصطفى فتحي (مكرر مكمل من المتوسط) </v>
+      </c>
+      <c r="B69" t="str">
+        <v xml:space="preserve">لغة انجليزية </v>
+      </c>
+      <c r="C69" t="str">
+        <v>12</v>
+      </c>
+      <c r="D69" t="str">
+        <v>8 حصص 2 ث 6 و7 + 4 تفكير ناقد صف 1ث نون 1و2 + مكمل (١٢) حصة بالمتوسط</v>
+      </c>
+      <c r="E69" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>إبراهيم شبكة</v>
+      </c>
+      <c r="B70" t="str">
+        <v xml:space="preserve">لغة انجليزية </v>
+      </c>
+      <c r="C70" t="str">
+        <v>24</v>
+      </c>
+      <c r="D70" t="str">
+        <v>24 حصة صف 3ث 7:2</v>
+      </c>
+      <c r="E70" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>احمد توفيق</v>
+      </c>
+      <c r="B71" t="str">
+        <v>تقنية -حاسب</v>
+      </c>
+      <c r="C71" t="str">
+        <v>24</v>
+      </c>
+      <c r="D71" t="str">
+        <v>20 حصة مجال صف 3 ث 5:1+ 4 حصص 1ث نون تقنية 1و2</v>
+      </c>
+      <c r="E71" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v xml:space="preserve">محمد مدحت </v>
+      </c>
+      <c r="B72" t="str">
+        <v>تقنية -حاسب</v>
+      </c>
+      <c r="C72" t="str">
+        <v>24</v>
+      </c>
+      <c r="D72" t="str">
+        <v xml:space="preserve">18 حصة 1ث كامل  + 6تفكير ناقد 1ث </v>
+      </c>
+      <c r="E72" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v xml:space="preserve">محمد صلاح </v>
+      </c>
+      <c r="B73" t="str">
+        <v xml:space="preserve">بدنية </v>
+      </c>
+      <c r="C73" t="str">
+        <v>28</v>
+      </c>
+      <c r="D73" t="str">
+        <v>12حصة 1ث كامل+12بدنية 3ث من  4:1 + 4 صف اول نون 1و2</v>
+      </c>
+      <c r="E73" t="str">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v xml:space="preserve">حسين عويضة </v>
+      </c>
+      <c r="B74" t="str">
+        <v xml:space="preserve">بدنية </v>
+      </c>
+      <c r="C74" t="str">
+        <v>13</v>
+      </c>
+      <c r="D74" t="str">
+        <v>9بدنية 3ث 7:5 + 8 مجال اختياري 3ث6 (م بالمتوسط بعد الفسحة) + مكمل (١٢) حصة بالمتوسط</v>
+      </c>
+      <c r="E74" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v xml:space="preserve">عيد العتيبي + (م .اداري)   </v>
+      </c>
+      <c r="B75" t="str">
+        <v xml:space="preserve">علم نفس </v>
+      </c>
+      <c r="C75" t="str">
+        <v>13</v>
+      </c>
+      <c r="D75" t="str">
+        <v xml:space="preserve"> 6 تفكير ناقد 1ث+ 7 نشاط 2ث + مكمل مراقب دور</v>
+      </c>
+      <c r="E75" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>محمد عبد الله</v>
+      </c>
+      <c r="B76" t="str">
+        <v>تقنية -حاسب</v>
+      </c>
+      <c r="C76" t="str">
+        <v>18</v>
+      </c>
+      <c r="D76" t="str">
+        <v>14 تقنية 3ث كامل + 4 مجال صف 3 ث 7+ مكمل (٨) حصص بالمتوسط</v>
+      </c>
+      <c r="E76" t="str">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="77" xml:space="preserve">
+      <c r="A77" t="str">
+        <v>إجمالي الحصص</v>
+      </c>
+      <c r="B77" t="str">
+        <v/>
+      </c>
+      <c r="C77" t="str">
+        <v/>
+      </c>
+      <c r="D77" t="str" xml:space="preserve">
+        <v xml:space="preserve">تخفيض حصة من اللغة الإنجليزية أول ثانوي_x000d_
+تخفيض حصة من اللغة الإنجليزيةوثان _x000d_
+تخفيض حصة تفكير ناقد أول ثانوي _x000d_
+تخفيض حصة نشاط صف ثان ثانوي_x000d_
+تخفيض حصة نشاط صف ثالث ثانوي _x000d_
+تخفيض حصة مجال صف ثالث ثانوي _x000d_
+عليه خروج جميع طلاب المدرسة بعد الحصة السادسة يوميا 11:50( بواقع تخفيض حصتين من كل فصل ) </v>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v/>
+      </c>
+      <c r="B78" t="str">
+        <v/>
+      </c>
+      <c r="C78" t="str">
+        <v/>
+      </c>
+      <c r="D78" t="str">
+        <v/>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v/>
+      </c>
+      <c r="B79" t="str">
+        <v>========================================</v>
+      </c>
+      <c r="C79" t="str">
+        <v/>
+      </c>
+      <c r="D79" t="str">
+        <v/>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v/>
+      </c>
+      <c r="B80" t="str">
+        <v>اسنادات قطاع البنات</v>
+      </c>
+      <c r="C80" t="str">
+        <v/>
+      </c>
+      <c r="D80" t="str">
+        <v/>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v/>
+      </c>
+      <c r="B81" t="str">
+        <v/>
+      </c>
+      <c r="C81" t="str">
+        <v/>
+      </c>
+      <c r="D81" t="str">
+        <v/>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v/>
+      </c>
+      <c r="B82" t="str">
+        <v>اسنادات ابتدائي (بنات)</v>
+      </c>
+      <c r="C82" t="str">
+        <v/>
+      </c>
+      <c r="D82" t="str">
+        <v/>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>المعلم</v>
+      </c>
+      <c r="B83" t="str">
+        <v>المادة</v>
+      </c>
+      <c r="C83" t="str">
+        <v xml:space="preserve">عدد حصص المعلم بالمرحلة </v>
+      </c>
+      <c r="D83" t="str">
+        <v>ملاحظات</v>
+      </c>
+      <c r="E83" t="str">
+        <v>إجمالي نصاب المعلم بعد الاكمال</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v/>
+      </c>
+      <c r="B84" t="str">
+        <v/>
+      </c>
+      <c r="C84" t="str">
+        <v/>
+      </c>
+      <c r="D84" t="str">
+        <v/>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v xml:space="preserve">نورا مجدي </v>
+      </c>
+      <c r="B85" t="str">
+        <v>انجليزي</v>
+      </c>
+      <c r="C85">
+        <v>24</v>
+      </c>
+      <c r="D85" t="str">
+        <v>(3) انجليزي وزاري ص1 ( 2) انجليزي اثرائي ص1 (1) ماث ص1 ( 1) ساينس ص1 ( 3) انجليزي وزاري ص2 (2) انجليزي اثرائي ص2 (6) انجليزي وزاري ص3 (4)انجليزي اثرائي ص3 (2) نشاط ص5</v>
+      </c>
+      <c r="E85">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v xml:space="preserve">سارة المخلفي </v>
+      </c>
+      <c r="B86" t="str">
+        <v>إسلامية</v>
+      </c>
+      <c r="C86">
+        <v>24</v>
+      </c>
+      <c r="D86" t="str">
+        <v>(10)اسلاميةص3(5)اسلاميةص4(5)إسلامية ص5(2)اجتماعيات ص5(2)نشاط ص4 + منسقة تطوع ابتدائي ومتوسط</v>
+      </c>
+      <c r="E86">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>نوير الشمري ( مكرر مكمل من الثانوي)</v>
+      </c>
+      <c r="B87" t="str">
+        <v>حاسب</v>
+      </c>
+      <c r="C87">
+        <v>8</v>
+      </c>
+      <c r="D87" t="str">
+        <v>(2) رقمية ص2 (2)رقمية ص4(2)رقمية ص5(2) رقمية ص6 + مسند (٦) حصص بالمتوسط + (10) حصة بالثانوي</v>
+      </c>
+      <c r="E87">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>نهال الشبرمي ( مكرر مكمل من المتوسط)</v>
+      </c>
+      <c r="B88" t="str">
+        <v>إسلامية</v>
+      </c>
+      <c r="C88">
+        <v>7</v>
+      </c>
+      <c r="D88" t="str">
+        <v>(2) بدنية ص6 (5) إسلامية ص6 + مسند (13) حصة بالمتوسط + (4) رقمية kg + منسقة الصيانة والمشتريات</v>
+      </c>
+      <c r="E88">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v xml:space="preserve">نوضا المطيري </v>
+      </c>
+      <c r="B89" t="str">
+        <v>رياضيات</v>
+      </c>
+      <c r="C89">
+        <v>24</v>
+      </c>
+      <c r="D89" t="str">
+        <v>(4)رياضيات ص1(3) علوم ص1 (3) علوم ص2 (6) رياضيات ص4 (2)اجتماعايت ص4 (1) اسرية ص4(1) نشاط ص3 فصل(4) رقمية ص3</v>
+      </c>
+      <c r="E89">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>الجوهرة المخلفي  ( مكرر مكمل من المتوسط)</v>
+      </c>
+      <c r="B90" t="str">
+        <v>لغة عربية</v>
+      </c>
+      <c r="C90">
+        <v>7</v>
+      </c>
+      <c r="D90" t="str">
+        <v>(5) لغتي ص6 (2) اجتماعيات ص6 + (17) حصة بالمتوسط + منسقة اختبارات مركزية</v>
+      </c>
+      <c r="E90">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>حنان العنزي (مكرر مكمل من متوسط )</v>
+      </c>
+      <c r="B91" t="str">
+        <v>انجليزي</v>
+      </c>
+      <c r="C91">
+        <v>3</v>
+      </c>
+      <c r="D91" t="str">
+        <v>(3) بدنية ص1 + مسند لها ( 11 ) متوسط + (11) ثانوي + منسقة اختبارات steep</v>
+      </c>
+      <c r="E91">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>أشواق العنزي</v>
+      </c>
+      <c r="B92" t="str">
+        <v xml:space="preserve"> لغة عربية</v>
+      </c>
+      <c r="C92">
+        <v>25</v>
+      </c>
+      <c r="D92" t="str">
+        <v>(8)لغتي ص1 (7)لغتي ص2 (5) إسلامية ص1(5) إسلامية ص2</v>
+      </c>
+      <c r="E92">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>ناهد بعزقي</v>
+      </c>
+      <c r="B93" t="str">
+        <v xml:space="preserve"> لغة عربية</v>
+      </c>
+      <c r="C93">
+        <v>24</v>
+      </c>
+      <c r="D93" t="str">
+        <v>(12) لغتي ص3 (5)لغتي ص4 (5) لغتي ص5 (1)اسرية ص5 (1) نشاط ص 3فصل</v>
+      </c>
+      <c r="E93">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>نوف الزلفي</v>
+      </c>
+      <c r="B94" t="str">
+        <v>رياضيات</v>
+      </c>
+      <c r="C94">
+        <v>24</v>
+      </c>
+      <c r="D94" t="str">
+        <v>(6)رياضيات ص2 (12) رياضيات ص3 (6) بدنية ص3 + معلمة موهبة</v>
+      </c>
+      <c r="E94">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>نور العيدة ( مكرر مكمل من الثانوي)</v>
+      </c>
+      <c r="B95" t="str">
+        <v>رياضيات</v>
+      </c>
+      <c r="C95">
+        <v>6</v>
+      </c>
+      <c r="D95" t="str">
+        <v xml:space="preserve"> ( 6 )  رياضيات ص6 + مسند ( 18) ثانوي + منسقة قدرات وتحصيلي</v>
+      </c>
+      <c r="E95">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>هدى المطيري ( مكرر مكمل من الثانوي)</v>
+      </c>
+      <c r="B96" t="str">
+        <v>كيمياء</v>
+      </c>
+      <c r="C96">
+        <v>2</v>
+      </c>
+      <c r="D96" t="str">
+        <v>(2) بدنية ص5 + مسند ( 23) ثانوي</v>
+      </c>
+      <c r="E96">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>سلطانة العتيبي ( مكرر مكمل من الثانوي)</v>
+      </c>
+      <c r="B97" t="str">
+        <v>فيزياء</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+      <c r="D97" t="str">
+        <v>(1) اسرية ص6 + ( 18 ) ثانوي + ( 5) متوسط</v>
+      </c>
+      <c r="E97">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>نوف العتيبي ( مكرر مكمل من الثانوي )</v>
+      </c>
+      <c r="B98" t="str">
+        <v>لغة عربية</v>
+      </c>
+      <c r="C98">
+        <v>2</v>
+      </c>
+      <c r="D98" t="str">
+        <v>(2) رقمية ص1 + (22) مسند ثانوي</v>
+      </c>
+      <c r="E98">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>بدور  البقمي  ( مكرر مكمل من المتوسط)</v>
+      </c>
+      <c r="B99" t="str">
+        <v>رياضيات</v>
+      </c>
+      <c r="C99">
+        <v>6</v>
+      </c>
+      <c r="D99" t="str">
+        <v>(6)رياضيات ص5 + مسند ( 18)  متوسط</v>
+      </c>
+      <c r="E99">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>منى الخلف</v>
+      </c>
+      <c r="B100" t="str">
+        <v>علوم</v>
+      </c>
+      <c r="C100">
+        <v>20</v>
+      </c>
+      <c r="D100" t="str">
+        <v xml:space="preserve"> (8) علوم ص3 (4) علوم ص4 (4) علوم ص5  (4) علوم ص6 + مسند (4) بالمتوسط</v>
+      </c>
+      <c r="E100">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v xml:space="preserve"> عهود الرويلي </v>
+      </c>
+      <c r="B101" t="str">
+        <v>انجليزي</v>
+      </c>
+      <c r="C101">
+        <v>20</v>
+      </c>
+      <c r="D101" t="str">
+        <v>(3) انجليزي وزاري ص4 ( 2) انجليزي اثرائي ص4  ( 3) انجليزي وزاري ص5 (2) انجليزي اثرائي ص5 (3) انجليزي وزاري ص6 (2)انجليزي اثرائي ص6 (3) بدنية ص2 (2) نشاط ص6 + (4) kg</v>
+      </c>
+      <c r="E101">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v xml:space="preserve">هدى البكري </v>
+      </c>
+      <c r="B102" t="str">
+        <v>فنية</v>
+      </c>
+      <c r="C102">
+        <v>18</v>
+      </c>
+      <c r="D102" t="str">
+        <v>(2)فنية ص1(2) فنية ص2(4) فنية ص3(1) فنية ص4(1)فنية ص5(1) قنية ص6  (2) بدنية ص4 (1)نشاط ص2 (1) اسرية ص1(1) اسرية ص2(2)اسرية ص3+ مسند (6) حصص بالمتوسط + موجهة صحية ابتدائي</v>
+      </c>
+      <c r="E102">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>إجمالي الحصص</v>
+      </c>
+      <c r="B103">
+        <v>245</v>
+      </c>
+      <c r="C103">
+        <v>245</v>
+      </c>
+      <c r="D103" t="str">
+        <v>تم زيادة ( 14) حصة لتفعيل المواد الاثرائية ورفع مستوى التحصيل فأصبح إجمالي الحصص في الأسبوع 35</v>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v/>
+      </c>
+      <c r="B104" t="str">
+        <v>اسنادات متوسط (بنات)</v>
+      </c>
+      <c r="C104" t="str">
+        <v/>
+      </c>
+      <c r="D104" t="str">
+        <v/>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>المعلم</v>
+      </c>
+      <c r="B105" t="str">
+        <v>المادة</v>
+      </c>
+      <c r="C105" t="str">
+        <v xml:space="preserve">عدد حصص المعلم بالمرحلة </v>
+      </c>
+      <c r="D105" t="str">
+        <v>ملاحظات</v>
+      </c>
+      <c r="E105" t="str">
+        <v>إجمالي نصاب المعلم بعد الاكمال</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v/>
+      </c>
+      <c r="B106" t="str">
+        <v/>
+      </c>
+      <c r="C106" t="str">
+        <v/>
+      </c>
+      <c r="D106" t="str">
+        <v/>
+      </c>
+      <c r="E106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>هدى البكري ( مكرر مكمل من ابتدائي)</v>
+      </c>
+      <c r="B107" t="str">
+        <v>فنية</v>
+      </c>
+      <c r="C107">
+        <v>6</v>
+      </c>
+      <c r="D107" t="str">
+        <v>(2) فنية ص1 (2) فنية ص2 (2) فنية ص + مسند (18) حصة بالابتدائي + موجهة صحية ابتدائي</v>
+      </c>
+      <c r="E107">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v xml:space="preserve">حنان الغربي </v>
+      </c>
+      <c r="B108" t="str">
+        <v>اجتماعيات</v>
+      </c>
+      <c r="C108">
+        <v>11</v>
+      </c>
+      <c r="D108" t="str">
+        <v>(3) اجتماعيات ص1 (3) اجتماعيات ص2(2) اجتماعيات ص3 (2) بدنية 3م (1) اسرية 3م + مسند (13) حصص بالثانوي + مسؤولة المقصف</v>
+      </c>
+      <c r="E108">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>نوير الشمري    ( مكرر مكمل من الثانوي)</v>
+      </c>
+      <c r="B109" t="str">
+        <v>حاسب</v>
+      </c>
+      <c r="C109">
+        <v>6</v>
+      </c>
+      <c r="D109" t="str">
+        <v>(2) رقمية ص1 (2) رقمية ص3 (2) رقمية ص3 + مسند (١0) حصص بالثانوي + (8) حصص بالابتدائي</v>
+      </c>
+      <c r="E109">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>منى الخلف ( مكرر مكمل من الابتدائي )</v>
+      </c>
+      <c r="B110" t="str">
+        <v>علوم</v>
+      </c>
+      <c r="C110">
+        <v>4</v>
+      </c>
+      <c r="D110" t="str">
+        <v>(4) علوم ص1 + مسند (20 ) ابتدائي</v>
+      </c>
+      <c r="E110">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>بدور  البقمي</v>
+      </c>
+      <c r="B111" t="str">
+        <v>رياضيات</v>
+      </c>
+      <c r="C111">
+        <v>18</v>
+      </c>
+      <c r="D111" t="str">
+        <v>(6) رياضيات ص1 (6) رياضيات ص2 (6) رياضيات ص3 + مسند لها (6) ابتدائي</v>
+      </c>
+      <c r="E111">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>ريم الحربي ( مكرر مكمل من الثانوي)</v>
+      </c>
+      <c r="B112" t="str">
+        <v>دين</v>
+      </c>
+      <c r="C112">
+        <v>5</v>
+      </c>
+      <c r="D112" t="str">
+        <v>( 5 ) إسلامية ص3 + مسند ثانوي 19 ثانوي</v>
+      </c>
+      <c r="E112">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>اماني فهمي ( مكرر مكمل من الثانوي)</v>
+      </c>
+      <c r="B113" t="str">
+        <v>احياء</v>
+      </c>
+      <c r="C113">
+        <v>4</v>
+      </c>
+      <c r="D113" t="str">
+        <v>(4) علوم ص2 + مسند لها (20) ثانوي</v>
+      </c>
+      <c r="E113">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>سلطانة العتيبي ( مكرر مكمل من الثانوي)</v>
+      </c>
+      <c r="B114" t="str">
+        <v>فيزياء</v>
+      </c>
+      <c r="C114">
+        <v>5</v>
+      </c>
+      <c r="D114" t="str">
+        <v>(4) علوم ص3 (1) نشاط ص3 + مسند لها (18 ) ثانوي + ( 1) ابتدائي + منسقة نافس</v>
+      </c>
+      <c r="E114">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>امل العنزي ( مكرر مكمل من الثانوي)</v>
+      </c>
+      <c r="B115" t="str">
+        <v>انجليزي</v>
+      </c>
+      <c r="C115">
+        <v>5</v>
+      </c>
+      <c r="D115" t="str">
+        <v>(4) انجليزي ص3 (1) أسرية ص3 + مسند (19) حصة بالثانوي + منسقة اختبارات steep</v>
+      </c>
+      <c r="E115">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>حنان العنزي</v>
+      </c>
+      <c r="B116" t="str">
+        <v>انجليزي</v>
+      </c>
+      <c r="C116">
+        <v>11</v>
+      </c>
+      <c r="D116" t="str">
+        <v>(4) انجليزي ص1(4) انجليزي ص2(1)اسرية ص2 (2) بدنية ص2+ مسند لها (11) حصة ثانوي+(3) ابتدائي</v>
+      </c>
+      <c r="E116">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>الجوهرة المخلفي</v>
+      </c>
+      <c r="B117" t="str">
+        <v>لغة عربية</v>
+      </c>
+      <c r="C117">
+        <v>17</v>
+      </c>
+      <c r="D117" t="str">
+        <v>(5) لغتي ص1 (5) لغتي ص2(4) لغتي ص3 (2) بدنية ص1 (1) نشاط ص1 + مسند (7) حصص بالابتدائي + منسقة اختبارات مركزية</v>
+      </c>
+      <c r="E117">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>نهال الشبرمي</v>
+      </c>
+      <c r="B118" t="str">
+        <v>إسلامية</v>
+      </c>
+      <c r="C118">
+        <v>13</v>
+      </c>
+      <c r="D118" t="str">
+        <v>(5) إسلامية ص1 (5) إسلامية ص2  (٢)  تفكير ناقد ص3  (1) نشاط ص2 + مسند (7) حصص بالابتدائي + (4) kg + منسقة الصيانة والمشتريات</v>
+      </c>
+      <c r="E118">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>إجمالي الحصص</v>
+      </c>
+      <c r="B119">
+        <v>105</v>
+      </c>
+      <c r="C119">
+        <v>105</v>
+      </c>
+      <c r="D119" t="str">
+        <v/>
+      </c>
+      <c r="E119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v/>
+      </c>
+      <c r="B120" t="str">
+        <v>اسنادات ثانوي (بنات)</v>
+      </c>
+      <c r="C120" t="str">
+        <v/>
+      </c>
+      <c r="D120" t="str">
+        <v/>
+      </c>
+      <c r="E120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>المعلم</v>
+      </c>
+      <c r="B121" t="str">
+        <v>المادة</v>
+      </c>
+      <c r="C121" t="str">
+        <v>عدد حصص المعلم بالمدرسة</v>
+      </c>
+      <c r="D121" t="str">
+        <v>الإسناد</v>
+      </c>
+      <c r="E121" t="str">
+        <v>إجمالي نصاب المعلم</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>حنان الغربي ( مكرر مكمل  متوسط )</v>
+      </c>
+      <c r="B122" t="str">
+        <v>اجتماعيات</v>
+      </c>
+      <c r="C122">
+        <v>13</v>
+      </c>
+      <c r="D122" t="str">
+        <v>(6) تاريخ ص2 (6) بدنية ص3 (1) نشاط ص3 فصل + مسند (11) حصص بالمتوسط + مسؤولة المقصف</v>
+      </c>
+      <c r="E122">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v xml:space="preserve">نوف العتيبي </v>
+      </c>
+      <c r="B123" t="str">
+        <v>لغة عربية</v>
+      </c>
+      <c r="C123">
+        <v>22</v>
+      </c>
+      <c r="D123" t="str">
+        <v>(8) كفايات ص1(8) كفايات ص2 (4) بحث ومعلومات ص3 (2) نشاط ص2  + مسند (2) ابتدائي + أمينة مصادر</v>
+      </c>
+      <c r="E123">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>ريم الحربي</v>
+      </c>
+      <c r="B124" t="str">
+        <v>إسلامية</v>
+      </c>
+      <c r="C124">
+        <v>19</v>
+      </c>
+      <c r="D124" t="str">
+        <v>(6) تفكير ناقد ص1 (8) قرآن وتفسيره صف1 (5) مجال اختياري مهارات إدارية + مسند (5) متوسط</v>
+      </c>
+      <c r="E124">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>سلطانة البقمي</v>
+      </c>
+      <c r="B125" t="str">
+        <v>رياضيات</v>
+      </c>
+      <c r="C125">
+        <v>25</v>
+      </c>
+      <c r="D125" t="str">
+        <v xml:space="preserve">(8) رياضيات ص3 (10) رياضيات ص1 ( 4) بدنية ص1 (3) نشاط ص3 </v>
+      </c>
+      <c r="E125">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>نور العيدة</v>
+      </c>
+      <c r="B126" t="str">
+        <v>رياضيات</v>
+      </c>
+      <c r="C126">
+        <v>18</v>
+      </c>
+      <c r="D126" t="str">
+        <v>(10) رياضيات ص2 (3) نشاط ص2 (5) مجال اختياري تنمية مستدامة ص3 + مسند (6) ابتدائي+ منسقة قدرات وتحصيلي</v>
+      </c>
+      <c r="E126">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>سلطانة العتيبي</v>
+      </c>
+      <c r="B127" t="str">
+        <v>فيزياء</v>
+      </c>
+      <c r="C127">
+        <v>18</v>
+      </c>
+      <c r="D127" t="str">
+        <v>(8) فيزياء ص2 (10) فيزياء ص3 + مسند (5) متوسط + (1) ابتدائي  + منسقة نافس</v>
+      </c>
+      <c r="E127">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>هدى المطيري</v>
+      </c>
+      <c r="B128" t="str">
+        <v>كيمياء</v>
+      </c>
+      <c r="C128">
+        <v>23</v>
+      </c>
+      <c r="D128" t="str">
+        <v>(6) كيمياء ص1 (10) كيمياء ص2 (6) كيمياء ص3 (1) نشاط ص1 فصل + (2) مسند ابتدائي</v>
+      </c>
+      <c r="E128">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>أماني فهمي</v>
+      </c>
+      <c r="B129" t="str">
+        <v>أحياء</v>
+      </c>
+      <c r="C129">
+        <v>20</v>
+      </c>
+      <c r="D129" t="str">
+        <v>(6) أحياء ص1 (8) أحياء ص2 (9) علم الأرض ص3 + مسند (4) متوسط</v>
+      </c>
+      <c r="E129">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>حنان العنزي (مكرر مكمل من متوسط )</v>
+      </c>
+      <c r="B130" t="str">
+        <v>انجليزي</v>
+      </c>
+      <c r="C130">
+        <v>11</v>
+      </c>
+      <c r="D130" t="str">
+        <v>(10) انجليزي ص1 (1) نشاط ص1 فصل + مسند (11) متوسط +( 3) ابتدائي</v>
+      </c>
+      <c r="E130">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v xml:space="preserve">أمل العنزي </v>
+      </c>
+      <c r="B131" t="str">
+        <v>انجليزي</v>
+      </c>
+      <c r="C131">
+        <v>19</v>
+      </c>
+      <c r="D131" t="str">
+        <v>(8) انجليزي ص3 (10) انجليزي ص2 (1) نشاط ص2 فصل + مسند (5) متوسط + منسقة اختبارات steep</v>
+      </c>
+      <c r="E131">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v xml:space="preserve">نوير الشمري </v>
+      </c>
+      <c r="B132" t="str">
+        <v>حاسب</v>
+      </c>
+      <c r="C132">
+        <v>10</v>
+      </c>
+      <c r="D132" t="str">
+        <v>(٦) تقنية رقمية ص1 (4) رقمية ص3  + مسند (٦) حصص بالمتوسط + (8) حصص بالابتدائي</v>
+      </c>
+      <c r="E132">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>إجمالي الحصص</v>
+      </c>
+      <c r="B133">
+        <v>198</v>
+      </c>
+      <c r="C133">
+        <v>198</v>
+      </c>
+      <c r="D133" t="str">
+        <v>تم زيادة ( 6) حصص لتفعيل البرامج الاثرائية ورفع مستوى التحصيل فأصبحت إجمالي الحصص 198</v>
+      </c>
+      <c r="E133" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E133"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N59"/>
